--- a/data/nzd0028/nzd0028.xlsx
+++ b/data/nzd0028/nzd0028.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN244"/>
+  <dimension ref="A1:AN245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31193,6 +31193,132 @@
         </is>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="n">
+        <v>386.98</v>
+      </c>
+      <c r="C245" t="n">
+        <v>398.34</v>
+      </c>
+      <c r="D245" t="n">
+        <v>400.83</v>
+      </c>
+      <c r="E245" t="n">
+        <v>412.9</v>
+      </c>
+      <c r="F245" t="n">
+        <v>409.05</v>
+      </c>
+      <c r="G245" t="n">
+        <v>407.48</v>
+      </c>
+      <c r="H245" t="n">
+        <v>415.13</v>
+      </c>
+      <c r="I245" t="n">
+        <v>416.76</v>
+      </c>
+      <c r="J245" t="n">
+        <v>416.46</v>
+      </c>
+      <c r="K245" t="n">
+        <v>413.58</v>
+      </c>
+      <c r="L245" t="n">
+        <v>414.78</v>
+      </c>
+      <c r="M245" t="n">
+        <v>414.83</v>
+      </c>
+      <c r="N245" t="n">
+        <v>410.94</v>
+      </c>
+      <c r="O245" t="n">
+        <v>406.11</v>
+      </c>
+      <c r="P245" t="n">
+        <v>403.45</v>
+      </c>
+      <c r="Q245" t="n">
+        <v>405.14</v>
+      </c>
+      <c r="R245" t="n">
+        <v>392.16</v>
+      </c>
+      <c r="S245" t="n">
+        <v>406.72</v>
+      </c>
+      <c r="T245" t="n">
+        <v>409.03</v>
+      </c>
+      <c r="U245" t="n">
+        <v>408.79</v>
+      </c>
+      <c r="V245" t="n">
+        <v>413.86</v>
+      </c>
+      <c r="W245" t="n">
+        <v>416.41</v>
+      </c>
+      <c r="X245" t="n">
+        <v>414.19</v>
+      </c>
+      <c r="Y245" t="n">
+        <v>415.1</v>
+      </c>
+      <c r="Z245" t="n">
+        <v>415.14</v>
+      </c>
+      <c r="AA245" t="n">
+        <v>411.39</v>
+      </c>
+      <c r="AB245" t="n">
+        <v>408.29</v>
+      </c>
+      <c r="AC245" t="n">
+        <v>405.19</v>
+      </c>
+      <c r="AD245" t="n">
+        <v>408.15</v>
+      </c>
+      <c r="AE245" t="n">
+        <v>411.25</v>
+      </c>
+      <c r="AF245" t="n">
+        <v>409.77</v>
+      </c>
+      <c r="AG245" t="n">
+        <v>414.87</v>
+      </c>
+      <c r="AH245" t="n">
+        <v>420.29</v>
+      </c>
+      <c r="AI245" t="n">
+        <v>424.69</v>
+      </c>
+      <c r="AJ245" t="n">
+        <v>416.15</v>
+      </c>
+      <c r="AK245" t="n">
+        <v>404.21</v>
+      </c>
+      <c r="AL245" t="n">
+        <v>405.35</v>
+      </c>
+      <c r="AM245" t="n">
+        <v>408.25</v>
+      </c>
+      <c r="AN245" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31204,7 +31330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B255"/>
+  <dimension ref="A1:B256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33757,6 +33883,16 @@
       </c>
       <c r="B255" t="n">
         <v>-0.26</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B256" t="n">
+        <v>0.44</v>
       </c>
     </row>
   </sheetData>
@@ -33925,28 +34061,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01520714517122228</v>
+        <v>0.01357547160252159</v>
       </c>
       <c r="J2" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K2" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001669760102035456</v>
+        <v>0.0001343090481025211</v>
       </c>
       <c r="M2" t="n">
-        <v>7.583746546497459</v>
+        <v>7.560684088339994</v>
       </c>
       <c r="N2" t="n">
-        <v>86.78119642387254</v>
+        <v>86.44317237650985</v>
       </c>
       <c r="O2" t="n">
-        <v>9.315642566343588</v>
+        <v>9.297482044968403</v>
       </c>
       <c r="P2" t="n">
-        <v>388.6712093797366</v>
+        <v>388.6856882904956</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34003,28 +34139,28 @@
         <v>0.0723</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1925382801321252</v>
+        <v>0.1888890880687662</v>
       </c>
       <c r="J3" t="n">
+        <v>244</v>
+      </c>
+      <c r="K3" t="n">
         <v>243</v>
       </c>
-      <c r="K3" t="n">
-        <v>242</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02766243452661099</v>
+        <v>0.02686929197696397</v>
       </c>
       <c r="M3" t="n">
-        <v>7.359027222196912</v>
+        <v>7.350131064299251</v>
       </c>
       <c r="N3" t="n">
-        <v>81.84138065296469</v>
+        <v>81.59314988376366</v>
       </c>
       <c r="O3" t="n">
-        <v>9.046622610287482</v>
+        <v>9.032892664244587</v>
       </c>
       <c r="P3" t="n">
-        <v>397.9796619922465</v>
+        <v>398.0120481063694</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34081,28 +34217,28 @@
         <v>0.0752</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1690388410236444</v>
+        <v>0.1667900305664007</v>
       </c>
       <c r="J4" t="n">
+        <v>244</v>
+      </c>
+      <c r="K4" t="n">
         <v>243</v>
       </c>
-      <c r="K4" t="n">
-        <v>242</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.02025451807295298</v>
+        <v>0.01990574948347856</v>
       </c>
       <c r="M4" t="n">
-        <v>7.3211080979861</v>
+        <v>7.302011770689042</v>
       </c>
       <c r="N4" t="n">
-        <v>86.81134268171363</v>
+        <v>86.48772805157982</v>
       </c>
       <c r="O4" t="n">
-        <v>9.317260470852665</v>
+        <v>9.299877851433308</v>
       </c>
       <c r="P4" t="n">
-        <v>399.2950683749913</v>
+        <v>399.3150262809729</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34159,28 +34295,28 @@
         <v>0.0809</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1547613943545514</v>
+        <v>0.15282416055641</v>
       </c>
       <c r="J5" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K5" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01654475038852243</v>
+        <v>0.01628631239491174</v>
       </c>
       <c r="M5" t="n">
-        <v>7.83324001961818</v>
+        <v>7.809659503977167</v>
       </c>
       <c r="N5" t="n">
-        <v>89.22293462708926</v>
+        <v>88.88212749784994</v>
       </c>
       <c r="O5" t="n">
-        <v>9.445789253793949</v>
+        <v>9.427731832092485</v>
       </c>
       <c r="P5" t="n">
-        <v>411.3370229944734</v>
+        <v>411.3542133417467</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34237,28 +34373,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.158501956877603</v>
+        <v>0.155861609961643</v>
       </c>
       <c r="J6" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K6" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01655519808387751</v>
+        <v>0.01615899142742971</v>
       </c>
       <c r="M6" t="n">
-        <v>7.699770099303109</v>
+        <v>7.681752391582145</v>
       </c>
       <c r="N6" t="n">
-        <v>93.52801487753079</v>
+        <v>93.19088506487668</v>
       </c>
       <c r="O6" t="n">
-        <v>9.670988309243828</v>
+        <v>9.653542617343991</v>
       </c>
       <c r="P6" t="n">
-        <v>408.2866013407601</v>
+        <v>408.3100308723174</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34315,28 +34451,28 @@
         <v>0.0759</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1115395679381861</v>
+        <v>0.107810187828324</v>
       </c>
       <c r="J7" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K7" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009702159530390331</v>
+        <v>0.009144942440913462</v>
       </c>
       <c r="M7" t="n">
-        <v>7.413068582668864</v>
+        <v>7.398133490905298</v>
       </c>
       <c r="N7" t="n">
-        <v>79.58151240431579</v>
+        <v>79.3474929890083</v>
       </c>
       <c r="O7" t="n">
-        <v>8.920847067645303</v>
+        <v>8.907720976153682</v>
       </c>
       <c r="P7" t="n">
-        <v>409.3434280403837</v>
+        <v>409.3765212784143</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34393,28 +34529,28 @@
         <v>0.0924</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.01190548359853285</v>
+        <v>-0.015876996602244</v>
       </c>
       <c r="J8" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K8" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001407346475745808</v>
+        <v>0.0002522231644057626</v>
       </c>
       <c r="M8" t="n">
-        <v>6.524924658570152</v>
+        <v>6.516095646966358</v>
       </c>
       <c r="N8" t="n">
-        <v>63.10863397301161</v>
+        <v>62.95447851833726</v>
       </c>
       <c r="O8" t="n">
-        <v>7.944094282736806</v>
+        <v>7.934385831199366</v>
       </c>
       <c r="P8" t="n">
-        <v>420.523273517388</v>
+        <v>420.5585153595443</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34471,28 +34607,28 @@
         <v>0.09080000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04125160407387283</v>
+        <v>-0.04485845460830909</v>
       </c>
       <c r="J9" t="n">
+        <v>244</v>
+      </c>
+      <c r="K9" t="n">
         <v>243</v>
       </c>
-      <c r="K9" t="n">
-        <v>242</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.001732895448071092</v>
+        <v>0.002065029199146307</v>
       </c>
       <c r="M9" t="n">
-        <v>6.39349111482095</v>
+        <v>6.382951973140342</v>
       </c>
       <c r="N9" t="n">
-        <v>61.56986286415088</v>
+        <v>61.40301066434141</v>
       </c>
       <c r="O9" t="n">
-        <v>7.846646599927314</v>
+        <v>7.836007316506373</v>
       </c>
       <c r="P9" t="n">
-        <v>422.4501231221017</v>
+        <v>422.4821334605559</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34549,28 +34685,28 @@
         <v>0.0839</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.03418266170256382</v>
+        <v>-0.03772173060768955</v>
       </c>
       <c r="J10" t="n">
+        <v>244</v>
+      </c>
+      <c r="K10" t="n">
         <v>243</v>
       </c>
-      <c r="K10" t="n">
-        <v>242</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.001225351406355268</v>
+        <v>0.001503861860001288</v>
       </c>
       <c r="M10" t="n">
-        <v>6.377590627311184</v>
+        <v>6.366917320514982</v>
       </c>
       <c r="N10" t="n">
-        <v>59.81783851345013</v>
+        <v>59.65497493248305</v>
       </c>
       <c r="O10" t="n">
-        <v>7.734199280691579</v>
+        <v>7.723663310404141</v>
       </c>
       <c r="P10" t="n">
-        <v>421.8800844084415</v>
+        <v>421.9114931935809</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34627,28 +34763,28 @@
         <v>0.067</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.05752594729320601</v>
+        <v>-0.0615804788567675</v>
       </c>
       <c r="J11" t="n">
+        <v>244</v>
+      </c>
+      <c r="K11" t="n">
         <v>243</v>
       </c>
-      <c r="K11" t="n">
-        <v>242</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.002918467193454011</v>
+        <v>0.003369378625966757</v>
       </c>
       <c r="M11" t="n">
-        <v>6.93882126323802</v>
+        <v>6.926792485390277</v>
       </c>
       <c r="N11" t="n">
-        <v>71.00934722753594</v>
+        <v>70.82646043140376</v>
       </c>
       <c r="O11" t="n">
-        <v>8.426704410832027</v>
+        <v>8.415845794179202</v>
       </c>
       <c r="P11" t="n">
-        <v>420.270156876289</v>
+        <v>420.3061403267769</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34705,28 +34841,28 @@
         <v>0.0711</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1176999603476663</v>
+        <v>-0.1204766868946064</v>
       </c>
       <c r="J12" t="n">
+        <v>244</v>
+      </c>
+      <c r="K12" t="n">
         <v>243</v>
       </c>
-      <c r="K12" t="n">
-        <v>242</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.01157347847593726</v>
+        <v>0.01222458463391796</v>
       </c>
       <c r="M12" t="n">
-        <v>7.169049506641539</v>
+        <v>7.152021485136955</v>
       </c>
       <c r="N12" t="n">
-        <v>74.30965072746463</v>
+        <v>74.05512816874798</v>
       </c>
       <c r="O12" t="n">
-        <v>8.620304561177907</v>
+        <v>8.605528930213877</v>
       </c>
       <c r="P12" t="n">
-        <v>421.4120106200061</v>
+        <v>421.4366537139502</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34783,28 +34919,28 @@
         <v>0.0689</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06490086574961858</v>
+        <v>-0.06875202342434378</v>
       </c>
       <c r="J13" t="n">
+        <v>244</v>
+      </c>
+      <c r="K13" t="n">
         <v>243</v>
       </c>
-      <c r="K13" t="n">
-        <v>242</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.004307377921918265</v>
+        <v>0.004868990357069003</v>
       </c>
       <c r="M13" t="n">
-        <v>6.28426552562307</v>
+        <v>6.275207687723579</v>
       </c>
       <c r="N13" t="n">
-        <v>61.15407436589648</v>
+        <v>61.00105114417799</v>
       </c>
       <c r="O13" t="n">
-        <v>7.820107055910198</v>
+        <v>7.810316968227218</v>
       </c>
       <c r="P13" t="n">
-        <v>421.452560283178</v>
+        <v>421.4867388163419</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34861,28 +34997,28 @@
         <v>0.0677</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.07127279820323294</v>
+        <v>-0.076090339218696</v>
       </c>
       <c r="J14" t="n">
+        <v>244</v>
+      </c>
+      <c r="K14" t="n">
         <v>243</v>
       </c>
-      <c r="K14" t="n">
-        <v>242</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.006218250380617296</v>
+        <v>0.007126368549828843</v>
       </c>
       <c r="M14" t="n">
-        <v>5.903898761719734</v>
+        <v>5.902459820412886</v>
       </c>
       <c r="N14" t="n">
-        <v>50.98970936472271</v>
+        <v>50.93422981423551</v>
       </c>
       <c r="O14" t="n">
-        <v>7.140707903613108</v>
+        <v>7.136822108910626</v>
       </c>
       <c r="P14" t="n">
-        <v>418.9734585263298</v>
+        <v>419.0162135883845</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -34939,28 +35075,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1280849972388189</v>
+        <v>-0.1332619878169004</v>
       </c>
       <c r="J15" t="n">
+        <v>244</v>
+      </c>
+      <c r="K15" t="n">
         <v>243</v>
       </c>
-      <c r="K15" t="n">
-        <v>242</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.02088180310290089</v>
+        <v>0.02269228102141929</v>
       </c>
       <c r="M15" t="n">
-        <v>5.521832329215057</v>
+        <v>5.5234644302794</v>
       </c>
       <c r="N15" t="n">
-        <v>48.31430731531143</v>
+        <v>48.29373057176467</v>
       </c>
       <c r="O15" t="n">
-        <v>6.950849395240227</v>
+        <v>6.949369077244687</v>
       </c>
       <c r="P15" t="n">
-        <v>416.0805329166261</v>
+        <v>416.1264780477028</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35017,28 +35153,28 @@
         <v>0.0746</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1192320077974294</v>
+        <v>-0.1249562088825961</v>
       </c>
       <c r="J16" t="n">
+        <v>244</v>
+      </c>
+      <c r="K16" t="n">
         <v>243</v>
       </c>
-      <c r="K16" t="n">
-        <v>242</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.01960584942473775</v>
+        <v>0.02158823572791746</v>
       </c>
       <c r="M16" t="n">
-        <v>5.407474614792751</v>
+        <v>5.41442598685804</v>
       </c>
       <c r="N16" t="n">
-        <v>44.64911637562133</v>
+        <v>44.68329592524124</v>
       </c>
       <c r="O16" t="n">
-        <v>6.681999429483763</v>
+        <v>6.684556524201231</v>
       </c>
       <c r="P16" t="n">
-        <v>413.8920929352424</v>
+        <v>413.9428944897751</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35095,28 +35231,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1512524601155846</v>
+        <v>-0.1578480360879928</v>
       </c>
       <c r="J17" t="n">
+        <v>244</v>
+      </c>
+      <c r="K17" t="n">
         <v>243</v>
       </c>
-      <c r="K17" t="n">
-        <v>242</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.02952860319060091</v>
+        <v>0.03217874139608379</v>
       </c>
       <c r="M17" t="n">
-        <v>5.504406614016445</v>
+        <v>5.5100091385836</v>
       </c>
       <c r="N17" t="n">
-        <v>47.22335469690301</v>
+        <v>47.31833714457967</v>
       </c>
       <c r="O17" t="n">
-        <v>6.871925108505113</v>
+        <v>6.878832542269049</v>
       </c>
       <c r="P17" t="n">
-        <v>417.5365844238821</v>
+        <v>417.5951193193987</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35173,28 +35309,28 @@
         <v>0.055</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1788767727064078</v>
+        <v>-0.1933919116651587</v>
       </c>
       <c r="J18" t="n">
+        <v>244</v>
+      </c>
+      <c r="K18" t="n">
         <v>243</v>
       </c>
-      <c r="K18" t="n">
-        <v>242</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.02820651444622579</v>
+        <v>0.03247673052061439</v>
       </c>
       <c r="M18" t="n">
-        <v>6.66535719064338</v>
+        <v>6.705891190259461</v>
       </c>
       <c r="N18" t="n">
-        <v>69.23800849687817</v>
+        <v>70.35431432130761</v>
       </c>
       <c r="O18" t="n">
-        <v>8.320937957759218</v>
+        <v>8.387747869440737</v>
       </c>
       <c r="P18" t="n">
-        <v>415.4073650777488</v>
+        <v>415.5361850846617</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35251,28 +35387,28 @@
         <v>0.0479</v>
       </c>
       <c r="I19" t="n">
-        <v>0.149628730875484</v>
+        <v>0.1459477891446473</v>
       </c>
       <c r="J19" t="n">
+        <v>244</v>
+      </c>
+      <c r="K19" t="n">
         <v>243</v>
       </c>
-      <c r="K19" t="n">
-        <v>242</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.01053720016121928</v>
+        <v>0.01011767408774455</v>
       </c>
       <c r="M19" t="n">
-        <v>9.08707429367724</v>
+        <v>9.06692446184511</v>
       </c>
       <c r="N19" t="n">
-        <v>132.0432883149485</v>
+        <v>131.5900131513249</v>
       </c>
       <c r="O19" t="n">
-        <v>11.49100902074959</v>
+        <v>11.47126902968128</v>
       </c>
       <c r="P19" t="n">
-        <v>407.5165278010007</v>
+        <v>407.5491956893729</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35329,28 +35465,28 @@
         <v>0.055</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01624434022857716</v>
+        <v>0.012642972403255</v>
       </c>
       <c r="J20" t="n">
+        <v>244</v>
+      </c>
+      <c r="K20" t="n">
         <v>243</v>
       </c>
-      <c r="K20" t="n">
-        <v>242</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.0002228743579955061</v>
+        <v>0.0001361499517145148</v>
       </c>
       <c r="M20" t="n">
-        <v>7.030604674793729</v>
+        <v>7.019991832386392</v>
       </c>
       <c r="N20" t="n">
-        <v>74.39841121698285</v>
+        <v>74.17805685293854</v>
       </c>
       <c r="O20" t="n">
-        <v>8.625451363087201</v>
+        <v>8.612668393299405</v>
       </c>
       <c r="P20" t="n">
-        <v>413.2017627206689</v>
+        <v>413.233629234419</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35407,28 +35543,28 @@
         <v>0.0839</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.06259465586755121</v>
+        <v>-0.06703494971837937</v>
       </c>
       <c r="J21" t="n">
+        <v>244</v>
+      </c>
+      <c r="K21" t="n">
         <v>243</v>
       </c>
-      <c r="K21" t="n">
-        <v>242</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.005531449760742047</v>
+        <v>0.006379843082421899</v>
       </c>
       <c r="M21" t="n">
-        <v>5.461357621148279</v>
+        <v>5.460863581397254</v>
       </c>
       <c r="N21" t="n">
-        <v>44.27778185758518</v>
+        <v>44.22679122997047</v>
       </c>
       <c r="O21" t="n">
-        <v>6.654155232453266</v>
+        <v>6.6503226410431</v>
       </c>
       <c r="P21" t="n">
-        <v>416.1137762297969</v>
+        <v>416.1531515423945</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -35485,28 +35621,28 @@
         <v>0.0838</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.04884764799459242</v>
+        <v>-0.0512952422621849</v>
       </c>
       <c r="J22" t="n">
+        <v>244</v>
+      </c>
+      <c r="K22" t="n">
         <v>243</v>
       </c>
-      <c r="K22" t="n">
-        <v>242</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.005178777488517028</v>
+        <v>0.00575365866613553</v>
       </c>
       <c r="M22" t="n">
-        <v>4.22831683920092</v>
+        <v>4.223166954900186</v>
       </c>
       <c r="N22" t="n">
-        <v>28.81140038705658</v>
+        <v>28.73270655003075</v>
       </c>
       <c r="O22" t="n">
-        <v>5.367625209257496</v>
+        <v>5.360289782281434</v>
       </c>
       <c r="P22" t="n">
-        <v>418.2674149135474</v>
+        <v>418.2891195107287</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -35563,28 +35699,28 @@
         <v>0.1942</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.08661990757084859</v>
+        <v>-0.08771831569103257</v>
       </c>
       <c r="J23" t="n">
+        <v>244</v>
+      </c>
+      <c r="K23" t="n">
         <v>243</v>
       </c>
-      <c r="K23" t="n">
-        <v>242</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.01646943983278992</v>
+        <v>0.01703545539792617</v>
       </c>
       <c r="M23" t="n">
-        <v>4.104571032267972</v>
+        <v>4.092660837349306</v>
       </c>
       <c r="N23" t="n">
-        <v>28.16460896520268</v>
+        <v>28.05673516353476</v>
       </c>
       <c r="O23" t="n">
-        <v>5.307033914080697</v>
+        <v>5.296860878249944</v>
       </c>
       <c r="P23" t="n">
-        <v>420.0769184107648</v>
+        <v>420.0866587938442</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -35641,28 +35777,28 @@
         <v>0.0851</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.08993276187817824</v>
+        <v>-0.09252270597725144</v>
       </c>
       <c r="J24" t="n">
+        <v>244</v>
+      </c>
+      <c r="K24" t="n">
         <v>243</v>
       </c>
-      <c r="K24" t="n">
-        <v>242</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.01398325257016508</v>
+        <v>0.01490811714907592</v>
       </c>
       <c r="M24" t="n">
-        <v>4.865334295079312</v>
+        <v>4.857592517312241</v>
       </c>
       <c r="N24" t="n">
-        <v>35.84851867122232</v>
+        <v>35.74563815529904</v>
       </c>
       <c r="O24" t="n">
-        <v>5.987363248644792</v>
+        <v>5.978765604646083</v>
       </c>
       <c r="P24" t="n">
-        <v>419.8603773826285</v>
+        <v>419.8833442992194</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -35719,28 +35855,28 @@
         <v>0.2</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.08409951019827656</v>
+        <v>-0.08606252852995327</v>
       </c>
       <c r="J25" t="n">
+        <v>244</v>
+      </c>
+      <c r="K25" t="n">
         <v>243</v>
       </c>
-      <c r="K25" t="n">
-        <v>242</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.01419181195203267</v>
+        <v>0.01497870967220549</v>
       </c>
       <c r="M25" t="n">
-        <v>4.361623982402031</v>
+        <v>4.35414789495622</v>
       </c>
       <c r="N25" t="n">
-        <v>30.88166938213226</v>
+        <v>30.7802311405529</v>
       </c>
       <c r="O25" t="n">
-        <v>5.557127799694034</v>
+        <v>5.547993433715734</v>
       </c>
       <c r="P25" t="n">
-        <v>419.81381478614</v>
+        <v>419.8312222963276</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -35797,28 +35933,28 @@
         <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.07111850919263135</v>
+        <v>-0.07412713284934486</v>
       </c>
       <c r="J26" t="n">
+        <v>244</v>
+      </c>
+      <c r="K26" t="n">
         <v>243</v>
       </c>
-      <c r="K26" t="n">
-        <v>242</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.01214150887349763</v>
+        <v>0.0132695199684657</v>
       </c>
       <c r="M26" t="n">
-        <v>3.836334207022136</v>
+        <v>3.836584424699763</v>
       </c>
       <c r="N26" t="n">
-        <v>25.86703359877204</v>
+        <v>25.8208298309188</v>
       </c>
       <c r="O26" t="n">
-        <v>5.085964372542541</v>
+        <v>5.081420060467232</v>
       </c>
       <c r="P26" t="n">
-        <v>420.8505483952388</v>
+        <v>420.8772280477463</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -35875,28 +36011,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.05943996542112473</v>
+        <v>-0.06389519390808183</v>
       </c>
       <c r="J27" t="n">
+        <v>244</v>
+      </c>
+      <c r="K27" t="n">
         <v>243</v>
       </c>
-      <c r="K27" t="n">
-        <v>242</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.007689361757914348</v>
+        <v>0.008917240054923226</v>
       </c>
       <c r="M27" t="n">
-        <v>4.079256360841764</v>
+        <v>4.084043630572381</v>
       </c>
       <c r="N27" t="n">
-        <v>28.65983681056102</v>
+        <v>28.67400176247861</v>
       </c>
       <c r="O27" t="n">
-        <v>5.353488284339569</v>
+        <v>5.354811085601304</v>
       </c>
       <c r="P27" t="n">
-        <v>418.6438590664314</v>
+        <v>418.6833668153013</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -35953,28 +36089,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1047389065306605</v>
+        <v>-0.1089561705539978</v>
       </c>
       <c r="J28" t="n">
+        <v>244</v>
+      </c>
+      <c r="K28" t="n">
         <v>243</v>
       </c>
-      <c r="K28" t="n">
-        <v>242</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.02261428639098662</v>
+        <v>0.02455736213516069</v>
       </c>
       <c r="M28" t="n">
-        <v>4.258016038686161</v>
+        <v>4.261372773978036</v>
       </c>
       <c r="N28" t="n">
-        <v>29.80289365374589</v>
+        <v>29.79861928380892</v>
       </c>
       <c r="O28" t="n">
-        <v>5.459202657325142</v>
+        <v>5.458811160299367</v>
       </c>
       <c r="P28" t="n">
-        <v>416.4228347185974</v>
+        <v>416.4602322636256</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -36031,28 +36167,28 @@
         <v>0.1413</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1352385612085471</v>
+        <v>-0.1396553807930828</v>
       </c>
       <c r="J29" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K29" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0436201805475126</v>
+        <v>0.0465695749934063</v>
       </c>
       <c r="M29" t="n">
-        <v>3.83676019853949</v>
+        <v>3.839874772128357</v>
       </c>
       <c r="N29" t="n">
-        <v>25.36374380409456</v>
+        <v>25.38959183450894</v>
       </c>
       <c r="O29" t="n">
-        <v>5.036243024725332</v>
+        <v>5.038808572917703</v>
       </c>
       <c r="P29" t="n">
-        <v>414.3853489140228</v>
+        <v>414.4244532846245</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -36109,28 +36245,28 @@
         <v>0.0956</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1172002414954041</v>
+        <v>-0.1208779901545062</v>
       </c>
       <c r="J30" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K30" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02663102979348408</v>
+        <v>0.02846284936282539</v>
       </c>
       <c r="M30" t="n">
-        <v>4.069743168136049</v>
+        <v>4.069350081788926</v>
       </c>
       <c r="N30" t="n">
-        <v>31.46323702971787</v>
+        <v>31.42389021080086</v>
       </c>
       <c r="O30" t="n">
-        <v>5.609210018328594</v>
+        <v>5.605701580605309</v>
       </c>
       <c r="P30" t="n">
-        <v>415.9187852794282</v>
+        <v>415.9514203577004</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -36187,28 +36323,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1278521443154394</v>
+        <v>-0.1329044663420991</v>
       </c>
       <c r="J31" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K31" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0318629669922158</v>
+        <v>0.03447655481010747</v>
       </c>
       <c r="M31" t="n">
-        <v>4.172745595347502</v>
+        <v>4.177759999172466</v>
       </c>
       <c r="N31" t="n">
-        <v>31.12601368572726</v>
+        <v>31.16754283603488</v>
       </c>
       <c r="O31" t="n">
-        <v>5.579069249052862</v>
+        <v>5.582789879266</v>
       </c>
       <c r="P31" t="n">
-        <v>421.0540997361977</v>
+        <v>421.0989323063593</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -36265,28 +36401,28 @@
         <v>0.0849</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1147929022211288</v>
+        <v>-0.1215361073816689</v>
       </c>
       <c r="J32" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K32" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L32" t="n">
-        <v>0.03097594822356209</v>
+        <v>0.03451994340533959</v>
       </c>
       <c r="M32" t="n">
-        <v>3.794172572524718</v>
+        <v>3.811739839617055</v>
       </c>
       <c r="N32" t="n">
-        <v>25.83431025570942</v>
+        <v>26.02964992061201</v>
       </c>
       <c r="O32" t="n">
-        <v>5.08274633005715</v>
+        <v>5.101926099093558</v>
       </c>
       <c r="P32" t="n">
-        <v>421.3984732816635</v>
+        <v>421.4583101679268</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -36343,28 +36479,28 @@
         <v>0.0956</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.03845627491040175</v>
+        <v>-0.04287059149482057</v>
       </c>
       <c r="J33" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K33" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L33" t="n">
-        <v>0.003338186874408677</v>
+        <v>0.004165012733387208</v>
       </c>
       <c r="M33" t="n">
-        <v>3.831857799984845</v>
+        <v>3.83391119305781</v>
       </c>
       <c r="N33" t="n">
-        <v>27.67122929146872</v>
+        <v>27.68690741414222</v>
       </c>
       <c r="O33" t="n">
-        <v>5.260344978370593</v>
+        <v>5.261834985453479</v>
       </c>
       <c r="P33" t="n">
-        <v>421.5215224373101</v>
+        <v>421.560693566336</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -36421,28 +36557,28 @@
         <v>0.0655</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.144864612587446</v>
+        <v>-0.1494904294902314</v>
       </c>
       <c r="J34" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K34" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0356603582995243</v>
+        <v>0.0380864450539139</v>
       </c>
       <c r="M34" t="n">
-        <v>4.31650883886251</v>
+        <v>4.321495919171641</v>
       </c>
       <c r="N34" t="n">
-        <v>35.56524363830966</v>
+        <v>35.56123508388973</v>
       </c>
       <c r="O34" t="n">
-        <v>5.963660255104214</v>
+        <v>5.963324163911411</v>
       </c>
       <c r="P34" t="n">
-        <v>429.9989517786914</v>
+        <v>430.0399996888909</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -36499,28 +36635,28 @@
         <v>0.0956</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1342330688808873</v>
+        <v>-0.1389962526583279</v>
       </c>
       <c r="J35" t="n">
+        <v>244</v>
+      </c>
+      <c r="K35" t="n">
         <v>243</v>
       </c>
-      <c r="K35" t="n">
-        <v>242</v>
-      </c>
       <c r="L35" t="n">
-        <v>0.0309670098803051</v>
+        <v>0.03329605346215836</v>
       </c>
       <c r="M35" t="n">
-        <v>4.338580862686856</v>
+        <v>4.340479812977148</v>
       </c>
       <c r="N35" t="n">
-        <v>35.4596749141195</v>
+        <v>35.46479359898292</v>
       </c>
       <c r="O35" t="n">
-        <v>5.954802676337773</v>
+        <v>5.955232455495161</v>
       </c>
       <c r="P35" t="n">
-        <v>434.298372599333</v>
+        <v>434.3405870539748</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -36577,28 +36713,28 @@
         <v>0.1394</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1883579872061588</v>
+        <v>-0.1924083781483915</v>
       </c>
       <c r="J36" t="n">
+        <v>244</v>
+      </c>
+      <c r="K36" t="n">
         <v>243</v>
       </c>
-      <c r="K36" t="n">
-        <v>242</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.05790371381882842</v>
+        <v>0.06063460077245875</v>
       </c>
       <c r="M36" t="n">
-        <v>4.796694396976123</v>
+        <v>4.794137490864726</v>
       </c>
       <c r="N36" t="n">
-        <v>36.30223598246855</v>
+        <v>36.26206366892329</v>
       </c>
       <c r="O36" t="n">
-        <v>6.025133690007928</v>
+        <v>6.021799039234312</v>
       </c>
       <c r="P36" t="n">
-        <v>426.259875818817</v>
+        <v>426.2957730364557</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -36655,28 +36791,28 @@
         <v>0.1224</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1511740930412604</v>
+        <v>-0.1579294109248859</v>
       </c>
       <c r="J37" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K37" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="L37" t="n">
-        <v>0.02814176149811909</v>
+        <v>0.03073383149981623</v>
       </c>
       <c r="M37" t="n">
-        <v>5.072146871918694</v>
+        <v>5.080324599215567</v>
       </c>
       <c r="N37" t="n">
-        <v>49.46103933901989</v>
+        <v>49.56063126607418</v>
       </c>
       <c r="O37" t="n">
-        <v>7.032854281088148</v>
+        <v>7.03993119753838</v>
       </c>
       <c r="P37" t="n">
-        <v>416.8033700539362</v>
+        <v>416.8633144243434</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -36733,28 +36869,28 @@
         <v>0.1069</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.06914878908548301</v>
+        <v>-0.07598938851432034</v>
       </c>
       <c r="J38" t="n">
+        <v>244</v>
+      </c>
+      <c r="K38" t="n">
         <v>243</v>
       </c>
-      <c r="K38" t="n">
-        <v>242</v>
-      </c>
       <c r="L38" t="n">
-        <v>0.005694680119143314</v>
+        <v>0.006892965796595041</v>
       </c>
       <c r="M38" t="n">
-        <v>5.582945955455312</v>
+        <v>5.585789005842937</v>
       </c>
       <c r="N38" t="n">
-        <v>52.47819037986292</v>
+        <v>52.57366981751657</v>
       </c>
       <c r="O38" t="n">
-        <v>7.24418320998737</v>
+        <v>7.250770291321921</v>
       </c>
       <c r="P38" t="n">
-        <v>415.9130115053021</v>
+        <v>415.9736720719028</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -36811,28 +36947,28 @@
         <v>0.2</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1589048048374668</v>
+        <v>-0.1666817374693232</v>
       </c>
       <c r="J39" t="n">
+        <v>244</v>
+      </c>
+      <c r="K39" t="n">
         <v>243</v>
       </c>
-      <c r="K39" t="n">
-        <v>242</v>
-      </c>
       <c r="L39" t="n">
-        <v>0.02678116803326536</v>
+        <v>0.02945822122952546</v>
       </c>
       <c r="M39" t="n">
-        <v>5.851232951561412</v>
+        <v>5.859848916959565</v>
       </c>
       <c r="N39" t="n">
-        <v>57.67854698133308</v>
+        <v>57.84371966527195</v>
       </c>
       <c r="O39" t="n">
-        <v>7.594639358213994</v>
+        <v>7.605505878327355</v>
       </c>
       <c r="P39" t="n">
-        <v>422.3572142519039</v>
+        <v>422.4261779655041</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -36870,7 +37006,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN244"/>
+  <dimension ref="A1:AN245"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86045,6 +86181,208 @@
         </is>
       </c>
     </row>
+    <row r="245">
+      <c r="A245" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-20 22:17:54+00:00</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>-34.86128684460865,173.29571035235736</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>-34.86149641317852,173.2965049625176</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>-34.86157507218155,173.29734789678574</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>-34.86161773110641,173.29820586071162</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>-34.86164056008273,173.29904387849575</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>-34.861644558299055,173.29995467195954</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>-34.861603519528394,173.3008410807367</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>-34.86154868108773,173.3016980082885</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>-34.86148069478389,173.30257882864063</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>-34.861430183994436,173.30348072186456</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>-34.86136082857001,173.30438462583115</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>-34.86131036159348,173.30527729442213</t>
+        </is>
+      </c>
+      <c r="N245" t="inlineStr">
+        <is>
+          <t>-34.861278808234296,173.30616927909523</t>
+        </is>
+      </c>
+      <c r="O245" t="inlineStr">
+        <is>
+          <t>-34.86125442463464,173.30707093970577</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>-34.86121733529272,173.307984599927</t>
+        </is>
+      </c>
+      <c r="Q245" t="inlineStr">
+        <is>
+          <t>-34.86118882781097,173.30888182973175</t>
+        </is>
+      </c>
+      <c r="R245" t="inlineStr">
+        <is>
+          <t>-34.861246713121815,173.30977039110476</t>
+        </is>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>-34.861040232751485,173.31065176264178</t>
+        </is>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>-34.86096798454995,173.31155740763063</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>-34.86092933602885,173.31245273025394</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>-34.860828409214484,173.3133348549018</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>-34.86074029720783,173.3142082474765</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>-34.86065746121339,173.31508922098905</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>-34.860552459320274,173.31598484597316</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>-34.86046658239018,173.31686679896058</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>-34.86037978674345,173.31774727945782</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>-34.86028792729376,173.3186434447255</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>-34.86020415084094,173.31955049734356</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>-34.86010194115979,173.32045227110592</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>-34.860002556795635,173.3213297110762</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>-34.85990565876567,173.32221071575407</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>-34.859759025701166,173.3231074300025</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>-34.85963799415225,173.32400027823445</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>-34.8595221871825,173.32481981476528</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>-34.859395254737976,173.32565227852507</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>-34.859284418311965,173.32658106144385</t>
+        </is>
+      </c>
+      <c r="AL245" t="inlineStr">
+        <is>
+          <t>-34.85915478467783,173.32750690489712</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>-34.859053956046054,173.328409812841</t>
+        </is>
+      </c>
+      <c r="AN245" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0028/nzd0028.xlsx
+++ b/data/nzd0028/nzd0028.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN245"/>
+  <dimension ref="A1:AN246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31319,6 +31319,132 @@
         </is>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="n">
+        <v>381.79</v>
+      </c>
+      <c r="C246" t="n">
+        <v>393.13</v>
+      </c>
+      <c r="D246" t="n">
+        <v>397.41</v>
+      </c>
+      <c r="E246" t="n">
+        <v>409.12</v>
+      </c>
+      <c r="F246" t="n">
+        <v>406.11</v>
+      </c>
+      <c r="G246" t="n">
+        <v>404.99</v>
+      </c>
+      <c r="H246" t="n">
+        <v>412.36</v>
+      </c>
+      <c r="I246" t="n">
+        <v>414.04</v>
+      </c>
+      <c r="J246" t="n">
+        <v>413.64</v>
+      </c>
+      <c r="K246" t="n">
+        <v>409.8</v>
+      </c>
+      <c r="L246" t="n">
+        <v>412.63</v>
+      </c>
+      <c r="M246" t="n">
+        <v>414.15</v>
+      </c>
+      <c r="N246" t="n">
+        <v>409.49</v>
+      </c>
+      <c r="O246" t="n">
+        <v>404.83</v>
+      </c>
+      <c r="P246" t="n">
+        <v>401.25</v>
+      </c>
+      <c r="Q246" t="n">
+        <v>402.38</v>
+      </c>
+      <c r="R246" t="n">
+        <v>396.05</v>
+      </c>
+      <c r="S246" t="n">
+        <v>404.61</v>
+      </c>
+      <c r="T246" t="n">
+        <v>406.38</v>
+      </c>
+      <c r="U246" t="n">
+        <v>407.03</v>
+      </c>
+      <c r="V246" t="n">
+        <v>411.98</v>
+      </c>
+      <c r="W246" t="n">
+        <v>413.82</v>
+      </c>
+      <c r="X246" t="n">
+        <v>410.59</v>
+      </c>
+      <c r="Y246" t="n">
+        <v>414.08</v>
+      </c>
+      <c r="Z246" t="n">
+        <v>412.65</v>
+      </c>
+      <c r="AA246" t="n">
+        <v>409.24</v>
+      </c>
+      <c r="AB246" t="n">
+        <v>405.4</v>
+      </c>
+      <c r="AC246" t="n">
+        <v>402.79</v>
+      </c>
+      <c r="AD246" t="n">
+        <v>405.52</v>
+      </c>
+      <c r="AE246" t="n">
+        <v>407.78</v>
+      </c>
+      <c r="AF246" t="n">
+        <v>408.38</v>
+      </c>
+      <c r="AG246" t="n">
+        <v>412.61</v>
+      </c>
+      <c r="AH246" t="n">
+        <v>418.93</v>
+      </c>
+      <c r="AI246" t="n">
+        <v>423.69</v>
+      </c>
+      <c r="AJ246" t="n">
+        <v>413.53</v>
+      </c>
+      <c r="AK246" t="n">
+        <v>402.08</v>
+      </c>
+      <c r="AL246" t="n">
+        <v>402.87</v>
+      </c>
+      <c r="AM246" t="n">
+        <v>407.29</v>
+      </c>
+      <c r="AN246" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31330,7 +31456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B256"/>
+  <dimension ref="A1:B257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33893,6 +34019,16 @@
       </c>
       <c r="B256" t="n">
         <v>0.44</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B257" t="n">
+        <v>-0.64</v>
       </c>
     </row>
   </sheetData>
@@ -34061,28 +34197,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01357547160252159</v>
+        <v>0.007932760040202054</v>
       </c>
       <c r="J2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K2" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001343090481025211</v>
+        <v>4.618782981458125e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>7.560684088339994</v>
+        <v>7.557513747291508</v>
       </c>
       <c r="N2" t="n">
-        <v>86.44317237650985</v>
+        <v>86.30230001748176</v>
       </c>
       <c r="O2" t="n">
-        <v>9.297482044968403</v>
+        <v>9.289903122071928</v>
       </c>
       <c r="P2" t="n">
-        <v>388.6856882904956</v>
+        <v>388.7360272501724</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34139,28 +34275,28 @@
         <v>0.0723</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1888890880687662</v>
+        <v>0.1812353472878894</v>
       </c>
       <c r="J3" t="n">
+        <v>245</v>
+      </c>
+      <c r="K3" t="n">
         <v>244</v>
       </c>
-      <c r="K3" t="n">
-        <v>243</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02686929197696397</v>
+        <v>0.02490142505563941</v>
       </c>
       <c r="M3" t="n">
-        <v>7.350131064299251</v>
+        <v>7.364863658411762</v>
       </c>
       <c r="N3" t="n">
-        <v>81.59314988376366</v>
+        <v>81.65023945200895</v>
       </c>
       <c r="O3" t="n">
-        <v>9.032892664244587</v>
+        <v>9.036052205028971</v>
       </c>
       <c r="P3" t="n">
-        <v>398.0120481063694</v>
+        <v>398.0803390237485</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34217,28 +34353,28 @@
         <v>0.0752</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1667900305664007</v>
+        <v>0.1619080706137632</v>
       </c>
       <c r="J4" t="n">
+        <v>245</v>
+      </c>
+      <c r="K4" t="n">
         <v>244</v>
       </c>
-      <c r="K4" t="n">
-        <v>243</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01990574948347856</v>
+        <v>0.01891975721796224</v>
       </c>
       <c r="M4" t="n">
-        <v>7.302011770689042</v>
+        <v>7.29571860575988</v>
       </c>
       <c r="N4" t="n">
-        <v>86.48772805157982</v>
+        <v>86.29254935281725</v>
       </c>
       <c r="O4" t="n">
-        <v>9.299877851433308</v>
+        <v>9.289378308197877</v>
       </c>
       <c r="P4" t="n">
-        <v>399.3150262809729</v>
+        <v>399.3585858335262</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34295,28 +34431,28 @@
         <v>0.0809</v>
       </c>
       <c r="I5" t="n">
-        <v>0.15282416055641</v>
+        <v>0.1479664385872003</v>
       </c>
       <c r="J5" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K5" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01628631239491174</v>
+        <v>0.01539925661394059</v>
       </c>
       <c r="M5" t="n">
-        <v>7.809659503977167</v>
+        <v>7.798857298483393</v>
       </c>
       <c r="N5" t="n">
-        <v>88.88212749784994</v>
+        <v>88.6764292017759</v>
       </c>
       <c r="O5" t="n">
-        <v>9.427731832092485</v>
+        <v>9.416816298610476</v>
       </c>
       <c r="P5" t="n">
-        <v>411.3542133417467</v>
+        <v>411.397549363379</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34373,28 +34509,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.155861609961643</v>
+        <v>0.1509682267445364</v>
       </c>
       <c r="J6" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K6" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01615899142742971</v>
+        <v>0.01529176434270518</v>
       </c>
       <c r="M6" t="n">
-        <v>7.681752391582145</v>
+        <v>7.67516687451326</v>
       </c>
       <c r="N6" t="n">
-        <v>93.19088506487668</v>
+        <v>92.96991485009369</v>
       </c>
       <c r="O6" t="n">
-        <v>9.653542617343991</v>
+        <v>9.642090792462685</v>
       </c>
       <c r="P6" t="n">
-        <v>408.3100308723174</v>
+        <v>408.3536850300267</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34451,28 +34587,28 @@
         <v>0.0759</v>
       </c>
       <c r="I7" t="n">
-        <v>0.107810187828324</v>
+        <v>0.1022015590573533</v>
       </c>
       <c r="J7" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K7" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L7" t="n">
-        <v>0.009144942440913462</v>
+        <v>0.0082816803909741</v>
       </c>
       <c r="M7" t="n">
-        <v>7.398133490905298</v>
+        <v>7.390831114525863</v>
       </c>
       <c r="N7" t="n">
-        <v>79.3474929890083</v>
+        <v>79.23302981889952</v>
       </c>
       <c r="O7" t="n">
-        <v>8.907720976153682</v>
+        <v>8.90129371602238</v>
       </c>
       <c r="P7" t="n">
-        <v>409.3765212784143</v>
+        <v>409.4265561835172</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34529,28 +34665,28 @@
         <v>0.0924</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.015876996602244</v>
+        <v>-0.0219293252638632</v>
       </c>
       <c r="J8" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K8" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0002522231644057626</v>
+        <v>0.0004837551129064366</v>
       </c>
       <c r="M8" t="n">
-        <v>6.516095646966358</v>
+        <v>6.516681468957945</v>
       </c>
       <c r="N8" t="n">
-        <v>62.95447851833726</v>
+        <v>62.94136817119256</v>
       </c>
       <c r="O8" t="n">
-        <v>7.934385831199366</v>
+        <v>7.933559615405468</v>
       </c>
       <c r="P8" t="n">
-        <v>420.5585153595443</v>
+        <v>420.6125085373071</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34607,28 +34743,28 @@
         <v>0.09080000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04485845460830909</v>
+        <v>-0.05050620513637558</v>
       </c>
       <c r="J9" t="n">
+        <v>245</v>
+      </c>
+      <c r="K9" t="n">
         <v>244</v>
       </c>
-      <c r="K9" t="n">
-        <v>243</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.002065029199146307</v>
+        <v>0.002631933305792589</v>
       </c>
       <c r="M9" t="n">
-        <v>6.382951973140342</v>
+        <v>6.381782553059991</v>
       </c>
       <c r="N9" t="n">
-        <v>61.40301066434141</v>
+        <v>61.36452680864165</v>
       </c>
       <c r="O9" t="n">
-        <v>7.836007316506373</v>
+        <v>7.833551353545954</v>
       </c>
       <c r="P9" t="n">
-        <v>422.4821334605559</v>
+        <v>422.5325258210672</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34685,28 +34821,28 @@
         <v>0.0839</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.03772173060768955</v>
+        <v>-0.04338241168471681</v>
       </c>
       <c r="J10" t="n">
+        <v>245</v>
+      </c>
+      <c r="K10" t="n">
         <v>244</v>
       </c>
-      <c r="K10" t="n">
-        <v>243</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.001503861860001288</v>
+        <v>0.001999768137187496</v>
       </c>
       <c r="M10" t="n">
-        <v>6.366917320514982</v>
+        <v>6.365384981035838</v>
       </c>
       <c r="N10" t="n">
-        <v>59.65497493248305</v>
+        <v>59.62463237234376</v>
       </c>
       <c r="O10" t="n">
-        <v>7.723663310404141</v>
+        <v>7.721698800933883</v>
       </c>
       <c r="P10" t="n">
-        <v>421.9114931935809</v>
+        <v>421.9620009276169</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34763,28 +34899,28 @@
         <v>0.067</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0615804788567675</v>
+        <v>-0.06849935293604152</v>
       </c>
       <c r="J11" t="n">
+        <v>245</v>
+      </c>
+      <c r="K11" t="n">
         <v>244</v>
       </c>
-      <c r="K11" t="n">
-        <v>243</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.003369378625966757</v>
+        <v>0.00418621098614369</v>
       </c>
       <c r="M11" t="n">
-        <v>6.926792485390277</v>
+        <v>6.92618649177435</v>
       </c>
       <c r="N11" t="n">
-        <v>70.82646043140376</v>
+        <v>70.85610813461918</v>
       </c>
       <c r="O11" t="n">
-        <v>8.415845794179202</v>
+        <v>8.417607031372942</v>
       </c>
       <c r="P11" t="n">
-        <v>420.3061403267769</v>
+        <v>420.36787435614</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34841,28 +34977,28 @@
         <v>0.0711</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1204766868946064</v>
+        <v>-0.1248664531287186</v>
       </c>
       <c r="J12" t="n">
+        <v>245</v>
+      </c>
+      <c r="K12" t="n">
         <v>244</v>
       </c>
-      <c r="K12" t="n">
-        <v>243</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.01222458463391796</v>
+        <v>0.01321995496968598</v>
       </c>
       <c r="M12" t="n">
-        <v>7.152021485136955</v>
+        <v>7.142143920531124</v>
       </c>
       <c r="N12" t="n">
-        <v>74.05512816874798</v>
+        <v>73.88040503236203</v>
       </c>
       <c r="O12" t="n">
-        <v>8.605528930213877</v>
+        <v>8.595371139884655</v>
       </c>
       <c r="P12" t="n">
-        <v>421.4366537139502</v>
+        <v>421.4758216413455</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -34919,28 +35055,28 @@
         <v>0.0689</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.06875202342434378</v>
+        <v>-0.07305673657325386</v>
       </c>
       <c r="J13" t="n">
+        <v>245</v>
+      </c>
+      <c r="K13" t="n">
         <v>244</v>
       </c>
-      <c r="K13" t="n">
-        <v>243</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.004868990357069003</v>
+        <v>0.005535020092398368</v>
       </c>
       <c r="M13" t="n">
-        <v>6.275207687723579</v>
+        <v>6.268092940007238</v>
       </c>
       <c r="N13" t="n">
-        <v>61.00105114417799</v>
+        <v>60.87488630569432</v>
       </c>
       <c r="O13" t="n">
-        <v>7.810316968227218</v>
+        <v>7.802235981159139</v>
       </c>
       <c r="P13" t="n">
-        <v>421.4867388163419</v>
+        <v>421.5251478529698</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -34997,28 +35133,28 @@
         <v>0.0677</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.076090339218696</v>
+        <v>-0.08194957896422216</v>
       </c>
       <c r="J14" t="n">
+        <v>245</v>
+      </c>
+      <c r="K14" t="n">
         <v>244</v>
       </c>
-      <c r="K14" t="n">
-        <v>243</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.007126368549828843</v>
+        <v>0.008297288863934438</v>
       </c>
       <c r="M14" t="n">
-        <v>5.902459820412886</v>
+        <v>5.906212603245481</v>
       </c>
       <c r="N14" t="n">
-        <v>50.93422981423551</v>
+        <v>50.95491454566947</v>
       </c>
       <c r="O14" t="n">
-        <v>7.136822108910626</v>
+        <v>7.138271117411377</v>
       </c>
       <c r="P14" t="n">
-        <v>419.0162135883845</v>
+        <v>419.0684929729132</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35075,28 +35211,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1332619878169004</v>
+        <v>-0.1393261335966032</v>
       </c>
       <c r="J15" t="n">
+        <v>245</v>
+      </c>
+      <c r="K15" t="n">
         <v>244</v>
       </c>
-      <c r="K15" t="n">
-        <v>243</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.02269228102141929</v>
+        <v>0.02485763605367486</v>
       </c>
       <c r="M15" t="n">
-        <v>5.5234644302794</v>
+        <v>5.529430290836632</v>
       </c>
       <c r="N15" t="n">
-        <v>48.29373057176467</v>
+        <v>48.34156472032595</v>
       </c>
       <c r="O15" t="n">
-        <v>6.949369077244687</v>
+        <v>6.952809843532753</v>
       </c>
       <c r="P15" t="n">
-        <v>416.1264780477028</v>
+        <v>416.1805857174388</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35153,28 +35289,28 @@
         <v>0.0746</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1249562088825961</v>
+        <v>-0.1322786143585905</v>
       </c>
       <c r="J16" t="n">
+        <v>245</v>
+      </c>
+      <c r="K16" t="n">
         <v>244</v>
       </c>
-      <c r="K16" t="n">
-        <v>243</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.02158823572791746</v>
+        <v>0.0241634533349574</v>
       </c>
       <c r="M16" t="n">
-        <v>5.41442598685804</v>
+        <v>5.429100296564533</v>
       </c>
       <c r="N16" t="n">
-        <v>44.68329592524124</v>
+        <v>44.85849356079898</v>
       </c>
       <c r="O16" t="n">
-        <v>6.684556524201231</v>
+        <v>6.697648360491836</v>
       </c>
       <c r="P16" t="n">
-        <v>413.9428944897751</v>
+        <v>414.0082290499195</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35231,28 +35367,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1578480360879928</v>
+        <v>-0.1664635482421771</v>
       </c>
       <c r="J17" t="n">
+        <v>245</v>
+      </c>
+      <c r="K17" t="n">
         <v>244</v>
       </c>
-      <c r="K17" t="n">
-        <v>243</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.03217874139608379</v>
+        <v>0.03562365839162784</v>
       </c>
       <c r="M17" t="n">
-        <v>5.5100091385836</v>
+        <v>5.524514789927566</v>
       </c>
       <c r="N17" t="n">
-        <v>47.31833714457967</v>
+        <v>47.62046797883267</v>
       </c>
       <c r="O17" t="n">
-        <v>6.878832542269049</v>
+        <v>6.900758507499931</v>
       </c>
       <c r="P17" t="n">
-        <v>417.5951193193987</v>
+        <v>417.6719916940382</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35309,28 +35445,28 @@
         <v>0.055</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1933919116651587</v>
+        <v>-0.204602785282093</v>
       </c>
       <c r="J18" t="n">
+        <v>245</v>
+      </c>
+      <c r="K18" t="n">
         <v>244</v>
       </c>
-      <c r="K18" t="n">
-        <v>243</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.03247673052061439</v>
+        <v>0.03612506286478312</v>
       </c>
       <c r="M18" t="n">
-        <v>6.705891190259461</v>
+        <v>6.731141398799693</v>
       </c>
       <c r="N18" t="n">
-        <v>70.35431432130761</v>
+        <v>70.90591947897785</v>
       </c>
       <c r="O18" t="n">
-        <v>8.387747869440737</v>
+        <v>8.420565270751</v>
       </c>
       <c r="P18" t="n">
-        <v>415.5361850846617</v>
+        <v>415.6362147127666</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35387,28 +35523,28 @@
         <v>0.0479</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1459477891446473</v>
+        <v>0.1406829290022802</v>
       </c>
       <c r="J19" t="n">
+        <v>245</v>
+      </c>
+      <c r="K19" t="n">
         <v>244</v>
       </c>
-      <c r="K19" t="n">
-        <v>243</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.01011767408774455</v>
+        <v>0.009482859157424417</v>
       </c>
       <c r="M19" t="n">
-        <v>9.06692446184511</v>
+        <v>9.054578186846724</v>
       </c>
       <c r="N19" t="n">
-        <v>131.5900131513249</v>
+        <v>131.2359538941242</v>
       </c>
       <c r="O19" t="n">
-        <v>11.47126902968128</v>
+        <v>11.45582619866957</v>
       </c>
       <c r="P19" t="n">
-        <v>407.5491956893729</v>
+        <v>407.5961716896438</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35465,28 +35601,28 @@
         <v>0.055</v>
       </c>
       <c r="I20" t="n">
-        <v>0.012642972403255</v>
+        <v>0.007038635148527836</v>
       </c>
       <c r="J20" t="n">
+        <v>245</v>
+      </c>
+      <c r="K20" t="n">
         <v>244</v>
       </c>
-      <c r="K20" t="n">
-        <v>243</v>
-      </c>
       <c r="L20" t="n">
-        <v>0.0001361499517145148</v>
+        <v>4.248546977370093e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>7.019991832386392</v>
+        <v>7.019695292975627</v>
       </c>
       <c r="N20" t="n">
-        <v>74.17805685293854</v>
+        <v>74.08289986027698</v>
       </c>
       <c r="O20" t="n">
-        <v>8.612668393299405</v>
+        <v>8.607142374811572</v>
       </c>
       <c r="P20" t="n">
-        <v>413.233629234419</v>
+        <v>413.2834845798675</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35543,28 +35679,28 @@
         <v>0.0839</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.06703494971837937</v>
+        <v>-0.07275768459341313</v>
       </c>
       <c r="J21" t="n">
+        <v>245</v>
+      </c>
+      <c r="K21" t="n">
         <v>244</v>
       </c>
-      <c r="K21" t="n">
-        <v>243</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.006379843082421899</v>
+        <v>0.007540659870333033</v>
       </c>
       <c r="M21" t="n">
-        <v>5.460863581397254</v>
+        <v>5.466805954147992</v>
       </c>
       <c r="N21" t="n">
-        <v>44.22679122997047</v>
+        <v>44.26456096219681</v>
       </c>
       <c r="O21" t="n">
-        <v>6.6503226410431</v>
+        <v>6.653161726742918</v>
       </c>
       <c r="P21" t="n">
-        <v>416.1531515423945</v>
+        <v>416.2041720433354</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -35621,28 +35757,28 @@
         <v>0.0838</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0512952422621849</v>
+        <v>-0.05515733467855588</v>
       </c>
       <c r="J22" t="n">
+        <v>245</v>
+      </c>
+      <c r="K22" t="n">
         <v>244</v>
       </c>
-      <c r="K22" t="n">
-        <v>243</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.00575365866613553</v>
+        <v>0.006686266423167941</v>
       </c>
       <c r="M22" t="n">
-        <v>4.223166954900186</v>
+        <v>4.224934971266312</v>
       </c>
       <c r="N22" t="n">
-        <v>28.73270655003075</v>
+        <v>28.71470483123568</v>
       </c>
       <c r="O22" t="n">
-        <v>5.360289782281434</v>
+        <v>5.358610345158125</v>
       </c>
       <c r="P22" t="n">
-        <v>418.2891195107287</v>
+        <v>418.3235516299979</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -35699,28 +35835,28 @@
         <v>0.1942</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.08771831569103257</v>
+        <v>-0.09080429229828287</v>
       </c>
       <c r="J23" t="n">
+        <v>245</v>
+      </c>
+      <c r="K23" t="n">
         <v>244</v>
       </c>
-      <c r="K23" t="n">
-        <v>243</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.01703545539792617</v>
+        <v>0.01836186705382925</v>
       </c>
       <c r="M23" t="n">
-        <v>4.092660837349306</v>
+        <v>4.089973639787621</v>
       </c>
       <c r="N23" t="n">
-        <v>28.05673516353476</v>
+        <v>28.00543921246204</v>
       </c>
       <c r="O23" t="n">
-        <v>5.296860878249944</v>
+        <v>5.292016554439531</v>
       </c>
       <c r="P23" t="n">
-        <v>420.0866587938442</v>
+        <v>420.1141715261011</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -35777,28 +35913,28 @@
         <v>0.0851</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.09252270597725144</v>
+        <v>-0.09786399059901595</v>
       </c>
       <c r="J24" t="n">
+        <v>245</v>
+      </c>
+      <c r="K24" t="n">
         <v>244</v>
       </c>
-      <c r="K24" t="n">
-        <v>243</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.01490811714907592</v>
+        <v>0.01671700359709416</v>
       </c>
       <c r="M24" t="n">
-        <v>4.857592517312241</v>
+        <v>4.862676548435877</v>
       </c>
       <c r="N24" t="n">
-        <v>35.74563815529904</v>
+        <v>35.78994122825979</v>
       </c>
       <c r="O24" t="n">
-        <v>5.978765604646083</v>
+        <v>5.982469492463776</v>
       </c>
       <c r="P24" t="n">
-        <v>419.8833442992194</v>
+        <v>419.9309640165437</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -35855,28 +35991,28 @@
         <v>0.2</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.08606252852995327</v>
+        <v>-0.08877996604239857</v>
       </c>
       <c r="J25" t="n">
+        <v>245</v>
+      </c>
+      <c r="K25" t="n">
         <v>244</v>
       </c>
-      <c r="K25" t="n">
-        <v>243</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.01497870967220549</v>
+        <v>0.01604765624044124</v>
       </c>
       <c r="M25" t="n">
-        <v>4.35414789495622</v>
+        <v>4.35061833355426</v>
       </c>
       <c r="N25" t="n">
-        <v>30.7802311405529</v>
+        <v>30.70346931502235</v>
       </c>
       <c r="O25" t="n">
-        <v>5.547993433715734</v>
+        <v>5.541071134268387</v>
       </c>
       <c r="P25" t="n">
-        <v>419.8312222963276</v>
+        <v>419.8554493531786</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -35933,28 +36069,28 @@
         <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.07412713284934486</v>
+        <v>-0.07901427137887451</v>
       </c>
       <c r="J26" t="n">
+        <v>245</v>
+      </c>
+      <c r="K26" t="n">
         <v>244</v>
       </c>
-      <c r="K26" t="n">
-        <v>243</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.0132695199684657</v>
+        <v>0.01509812686160461</v>
       </c>
       <c r="M26" t="n">
-        <v>3.836584424699763</v>
+        <v>3.84676758515691</v>
       </c>
       <c r="N26" t="n">
-        <v>25.8208298309188</v>
+        <v>25.87474166985091</v>
       </c>
       <c r="O26" t="n">
-        <v>5.081420060467232</v>
+        <v>5.086722094812229</v>
       </c>
       <c r="P26" t="n">
-        <v>420.8772280477463</v>
+        <v>420.9207988685844</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -36011,28 +36147,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.06389519390808183</v>
+        <v>-0.06993277585771449</v>
       </c>
       <c r="J27" t="n">
+        <v>245</v>
+      </c>
+      <c r="K27" t="n">
         <v>244</v>
       </c>
-      <c r="K27" t="n">
-        <v>243</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.008917240054923226</v>
+        <v>0.01067332313184588</v>
       </c>
       <c r="M27" t="n">
-        <v>4.084043630572381</v>
+        <v>4.0973000132721</v>
       </c>
       <c r="N27" t="n">
-        <v>28.67400176247861</v>
+        <v>28.80027577579435</v>
       </c>
       <c r="O27" t="n">
-        <v>5.354811085601304</v>
+        <v>5.366588839830601</v>
       </c>
       <c r="P27" t="n">
-        <v>418.6833668153013</v>
+        <v>418.7371943055256</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -36089,28 +36225,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1089561705539978</v>
+        <v>-0.1153302801701613</v>
       </c>
       <c r="J28" t="n">
+        <v>245</v>
+      </c>
+      <c r="K28" t="n">
         <v>244</v>
       </c>
-      <c r="K28" t="n">
-        <v>243</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.02455736213516069</v>
+        <v>0.02744264510568928</v>
       </c>
       <c r="M28" t="n">
-        <v>4.261372773978036</v>
+        <v>4.276184689888354</v>
       </c>
       <c r="N28" t="n">
-        <v>29.79861928380892</v>
+        <v>29.94821879859844</v>
       </c>
       <c r="O28" t="n">
-        <v>5.458811160299367</v>
+        <v>5.472496578217153</v>
       </c>
       <c r="P28" t="n">
-        <v>416.4602322636256</v>
+        <v>416.517060034398</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -36167,28 +36303,28 @@
         <v>0.1413</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1396553807930828</v>
+        <v>-0.145852100473387</v>
       </c>
       <c r="J29" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K29" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0465695749934063</v>
+        <v>0.05054291193603144</v>
       </c>
       <c r="M29" t="n">
-        <v>3.839874772128357</v>
+        <v>3.850781588204146</v>
       </c>
       <c r="N29" t="n">
-        <v>25.38959183450894</v>
+        <v>25.54394531277557</v>
       </c>
       <c r="O29" t="n">
-        <v>5.038808572917703</v>
+        <v>5.054101830471519</v>
       </c>
       <c r="P29" t="n">
-        <v>414.4244532846245</v>
+        <v>414.4796149438885</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -36245,28 +36381,28 @@
         <v>0.0956</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1208779901545062</v>
+        <v>-0.1265215303729594</v>
       </c>
       <c r="J30" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K30" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L30" t="n">
-        <v>0.02846284936282539</v>
+        <v>0.03118008458573773</v>
       </c>
       <c r="M30" t="n">
-        <v>4.069350081788926</v>
+        <v>4.078587446752754</v>
       </c>
       <c r="N30" t="n">
-        <v>31.42389021080086</v>
+        <v>31.50764860852415</v>
       </c>
       <c r="O30" t="n">
-        <v>5.605701580605309</v>
+        <v>5.613167431007572</v>
       </c>
       <c r="P30" t="n">
-        <v>415.9514203577004</v>
+        <v>416.0017667098671</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -36323,28 +36459,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1329044663420991</v>
+        <v>-0.1405496139507131</v>
       </c>
       <c r="J31" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K31" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L31" t="n">
-        <v>0.03447655481010747</v>
+        <v>0.03829026852739636</v>
       </c>
       <c r="M31" t="n">
-        <v>4.177759999172466</v>
+        <v>4.194020909082943</v>
       </c>
       <c r="N31" t="n">
-        <v>31.16754283603488</v>
+        <v>31.42941261520693</v>
       </c>
       <c r="O31" t="n">
-        <v>5.582789879266</v>
+        <v>5.606194129282978</v>
       </c>
       <c r="P31" t="n">
-        <v>421.0989323063593</v>
+        <v>421.1671351150522</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -36401,28 +36537,28 @@
         <v>0.0849</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1215361073816689</v>
+        <v>-0.1292287066315607</v>
       </c>
       <c r="J32" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K32" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L32" t="n">
-        <v>0.03451994340533959</v>
+        <v>0.0386439654905909</v>
       </c>
       <c r="M32" t="n">
-        <v>3.811739839617055</v>
+        <v>3.836083420650277</v>
       </c>
       <c r="N32" t="n">
-        <v>26.02964992061201</v>
+        <v>26.31733558989691</v>
       </c>
       <c r="O32" t="n">
-        <v>5.101926099093558</v>
+        <v>5.13004245497997</v>
       </c>
       <c r="P32" t="n">
-        <v>421.4583101679268</v>
+        <v>421.5269362954852</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -36479,28 +36615,28 @@
         <v>0.0956</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.04287059149482057</v>
+        <v>-0.04895574981901817</v>
       </c>
       <c r="J33" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K33" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L33" t="n">
-        <v>0.004165012733387208</v>
+        <v>0.005427525194508842</v>
       </c>
       <c r="M33" t="n">
-        <v>3.83391119305781</v>
+        <v>3.842969883298862</v>
       </c>
       <c r="N33" t="n">
-        <v>27.68690741414222</v>
+        <v>27.82039890823049</v>
       </c>
       <c r="O33" t="n">
-        <v>5.261834985453479</v>
+        <v>5.274504612589745</v>
       </c>
       <c r="P33" t="n">
-        <v>421.560693566336</v>
+        <v>421.6149796194376</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -36557,28 +36693,28 @@
         <v>0.0655</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1494904294902314</v>
+        <v>-0.1550830027278247</v>
       </c>
       <c r="J34" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K34" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0380864450539139</v>
+        <v>0.04101251713346343</v>
       </c>
       <c r="M34" t="n">
-        <v>4.321495919171641</v>
+        <v>4.330944217863988</v>
       </c>
       <c r="N34" t="n">
-        <v>35.56123508388973</v>
+        <v>35.62429414882867</v>
       </c>
       <c r="O34" t="n">
-        <v>5.963324163911411</v>
+        <v>5.968609063159412</v>
       </c>
       <c r="P34" t="n">
-        <v>430.0399996888909</v>
+        <v>430.0898913616422</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -36635,28 +36771,28 @@
         <v>0.0956</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1389962526583279</v>
+        <v>-0.1444394737097919</v>
       </c>
       <c r="J35" t="n">
+        <v>245</v>
+      </c>
+      <c r="K35" t="n">
         <v>244</v>
       </c>
-      <c r="K35" t="n">
-        <v>243</v>
-      </c>
       <c r="L35" t="n">
-        <v>0.03329605346215836</v>
+        <v>0.03599328765950693</v>
       </c>
       <c r="M35" t="n">
-        <v>4.340479812977148</v>
+        <v>4.345524074017476</v>
       </c>
       <c r="N35" t="n">
-        <v>35.46479359898292</v>
+        <v>35.51765767068956</v>
       </c>
       <c r="O35" t="n">
-        <v>5.955232455495161</v>
+        <v>5.95966925849829</v>
       </c>
       <c r="P35" t="n">
-        <v>434.3405870539748</v>
+        <v>434.3890879132726</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -36713,28 +36849,28 @@
         <v>0.1394</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1924083781483915</v>
+        <v>-0.1984103059514691</v>
       </c>
       <c r="J36" t="n">
+        <v>245</v>
+      </c>
+      <c r="K36" t="n">
         <v>244</v>
       </c>
-      <c r="K36" t="n">
-        <v>243</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.06063460077245875</v>
+        <v>0.06439852117673706</v>
       </c>
       <c r="M36" t="n">
-        <v>4.794137490864726</v>
+        <v>4.799567361035094</v>
       </c>
       <c r="N36" t="n">
-        <v>36.26206366892329</v>
+        <v>36.35443843570152</v>
       </c>
       <c r="O36" t="n">
-        <v>6.021799039234312</v>
+        <v>6.029464191427089</v>
       </c>
       <c r="P36" t="n">
-        <v>426.2957730364557</v>
+        <v>426.3492521535338</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -36791,28 +36927,28 @@
         <v>0.1224</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1579294109248859</v>
+        <v>-0.1662040680428202</v>
       </c>
       <c r="J37" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K37" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L37" t="n">
-        <v>0.03073383149981623</v>
+        <v>0.03393579296052263</v>
       </c>
       <c r="M37" t="n">
-        <v>5.080324599215567</v>
+        <v>5.094548924415968</v>
       </c>
       <c r="N37" t="n">
-        <v>49.56063126607418</v>
+        <v>49.8141404376816</v>
       </c>
       <c r="O37" t="n">
-        <v>7.03993119753838</v>
+        <v>7.057913320357626</v>
       </c>
       <c r="P37" t="n">
-        <v>416.8633144243434</v>
+        <v>416.9371331241651</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -36869,28 +37005,28 @@
         <v>0.1069</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.07598938851432034</v>
+        <v>-0.08462491230520647</v>
       </c>
       <c r="J38" t="n">
+        <v>245</v>
+      </c>
+      <c r="K38" t="n">
         <v>244</v>
       </c>
-      <c r="K38" t="n">
-        <v>243</v>
-      </c>
       <c r="L38" t="n">
-        <v>0.006892965796595041</v>
+        <v>0.008534286591950213</v>
       </c>
       <c r="M38" t="n">
-        <v>5.585789005842937</v>
+        <v>5.595167069475509</v>
       </c>
       <c r="N38" t="n">
-        <v>52.57366981751657</v>
+        <v>52.85693674197693</v>
       </c>
       <c r="O38" t="n">
-        <v>7.250770291321921</v>
+        <v>7.270277624821278</v>
       </c>
       <c r="P38" t="n">
-        <v>415.9736720719028</v>
+        <v>416.0506612666358</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -36947,28 +37083,28 @@
         <v>0.2</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1666817374693232</v>
+        <v>-0.1750485832762727</v>
       </c>
       <c r="J39" t="n">
+        <v>245</v>
+      </c>
+      <c r="K39" t="n">
         <v>244</v>
       </c>
-      <c r="K39" t="n">
-        <v>243</v>
-      </c>
       <c r="L39" t="n">
-        <v>0.02945822122952546</v>
+        <v>0.03243431367062632</v>
       </c>
       <c r="M39" t="n">
-        <v>5.859848916959565</v>
+        <v>5.870747353996865</v>
       </c>
       <c r="N39" t="n">
-        <v>57.84371966527195</v>
+        <v>58.07483655690921</v>
       </c>
       <c r="O39" t="n">
-        <v>7.605505878327355</v>
+        <v>7.620684782675977</v>
       </c>
       <c r="P39" t="n">
-        <v>422.4261779655041</v>
+        <v>422.50077178711</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -37006,7 +37142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN245"/>
+  <dimension ref="A1:AN246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86383,6 +86519,208 @@
         </is>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-30 22:18:00+00:00</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>-34.86132888332452,173.2956853975322</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>-34.861541277870536,173.29648804605858</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>-34.86160541589106,173.29734121096246</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>-34.86165165606265,173.29820184066116</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>-34.861667068531226,173.2990443774915</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>-34.86166701087218,173.2999543949673</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>-34.86162849657644,173.30084142400432</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>-34.86157313208911,173.30170036082305</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>-34.86150599099165,173.30258198361508</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>-34.861464123100184,173.30348456196322</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>-34.86138016109201,173.30438640008148</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>-34.86131647307432,173.30527790164584</t>
+        </is>
+      </c>
+      <c r="N246" t="inlineStr">
+        <is>
+          <t>-34.86129182655689,173.30617076050834</t>
+        </is>
+      </c>
+      <c r="O246" t="inlineStr">
+        <is>
+          <t>-34.86126592166126,173.30707218119116</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>-34.86123714728853,173.30798584672002</t>
+        </is>
+      </c>
+      <c r="Q246" t="inlineStr">
+        <is>
+          <t>-34.86121368292064,173.30888339244598</t>
+        </is>
+      </c>
+      <c r="R246" t="inlineStr">
+        <is>
+          <t>-34.86121179032046,173.30976638837612</t>
+        </is>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>-34.8610591863245,173.31065378932885</t>
+        </is>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>-34.86099183168088,173.31155927077944</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>-34.86094517036809,173.31245403647384</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>-34.860845300181445,173.31333661287636</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>-34.86076348920463,173.31421159410135</t>
+        </is>
+      </c>
+      <c r="X246" t="inlineStr">
+        <is>
+          <t>-34.86068961394215,173.3150946549299</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>-34.86056158363184,173.31598625476477</t>
+        </is>
+      </c>
+      <c r="Z246" t="inlineStr">
+        <is>
+          <t>-34.860488803016516,173.31687071385005</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>-34.860398907043034,173.3177511728032</t>
+        </is>
+      </c>
+      <c r="AB246" t="inlineStr">
+        <is>
+          <t>-34.86031366346309,173.31864841903015</t>
+        </is>
+      </c>
+      <c r="AC246" t="inlineStr">
+        <is>
+          <t>-34.86022561704919,173.31955383830305</t>
+        </is>
+      </c>
+      <c r="AD246" t="inlineStr">
+        <is>
+          <t>-34.860125533155056,173.32045521152705</t>
+        </is>
+      </c>
+      <c r="AE246" t="inlineStr">
+        <is>
+          <t>-34.860033593650044,173.32133453871907</t>
+        </is>
+      </c>
+      <c r="AF246" t="inlineStr">
+        <is>
+          <t>-34.85991806035251,173.32221292355806</t>
+        </is>
+      </c>
+      <c r="AG246" t="inlineStr">
+        <is>
+          <t>-34.85977926172149,173.3231103604</t>
+        </is>
+      </c>
+      <c r="AH246" t="inlineStr">
+        <is>
+          <t>-34.85965018501161,173.3240018993217</t>
+        </is>
+      </c>
+      <c r="AI246" t="inlineStr">
+        <is>
+          <t>-34.85953101253464,173.32482206141577</t>
+        </is>
+      </c>
+      <c r="AJ246" t="inlineStr">
+        <is>
+          <t>-34.8594178851824,173.32566051119855</t>
+        </is>
+      </c>
+      <c r="AK246" t="inlineStr">
+        <is>
+          <t>-34.85930315342304,173.32658619696437</t>
+        </is>
+      </c>
+      <c r="AL246" t="inlineStr">
+        <is>
+          <t>-34.85917696106814,173.32751040740033</t>
+        </is>
+      </c>
+      <c r="AM246" t="inlineStr">
+        <is>
+          <t>-34.85906256767936,173.3284108848413</t>
+        </is>
+      </c>
+      <c r="AN246" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0028/nzd0028.xlsx
+++ b/data/nzd0028/nzd0028.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN246"/>
+  <dimension ref="A1:AN248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31445,6 +31445,258 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="n">
+        <v>380.69</v>
+      </c>
+      <c r="C247" t="n">
+        <v>390.74</v>
+      </c>
+      <c r="D247" t="n">
+        <v>394.91</v>
+      </c>
+      <c r="E247" t="n">
+        <v>406.56</v>
+      </c>
+      <c r="F247" t="n">
+        <v>405.13</v>
+      </c>
+      <c r="G247" t="n">
+        <v>404.59</v>
+      </c>
+      <c r="H247" t="n">
+        <v>413.8</v>
+      </c>
+      <c r="I247" t="n">
+        <v>415.56</v>
+      </c>
+      <c r="J247" t="n">
+        <v>414.21</v>
+      </c>
+      <c r="K247" t="n">
+        <v>410.03</v>
+      </c>
+      <c r="L247" t="n">
+        <v>412.53</v>
+      </c>
+      <c r="M247" t="n">
+        <v>413.91</v>
+      </c>
+      <c r="N247" t="n">
+        <v>410.87</v>
+      </c>
+      <c r="O247" t="n">
+        <v>407.32</v>
+      </c>
+      <c r="P247" t="n">
+        <v>403.86</v>
+      </c>
+      <c r="Q247" t="n">
+        <v>403.68</v>
+      </c>
+      <c r="R247" t="n">
+        <v>402.33</v>
+      </c>
+      <c r="S247" t="n">
+        <v>401.52</v>
+      </c>
+      <c r="T247" t="n">
+        <v>404.25</v>
+      </c>
+      <c r="U247" t="n">
+        <v>408.85</v>
+      </c>
+      <c r="V247" t="n">
+        <v>411.01</v>
+      </c>
+      <c r="W247" t="n">
+        <v>413.01</v>
+      </c>
+      <c r="X247" t="n">
+        <v>409.35</v>
+      </c>
+      <c r="Y247" t="n">
+        <v>412.38</v>
+      </c>
+      <c r="Z247" t="n">
+        <v>413.35</v>
+      </c>
+      <c r="AA247" t="n">
+        <v>408.37</v>
+      </c>
+      <c r="AB247" t="n">
+        <v>405.51</v>
+      </c>
+      <c r="AC247" t="n">
+        <v>405.05</v>
+      </c>
+      <c r="AD247" t="n">
+        <v>405.37</v>
+      </c>
+      <c r="AE247" t="n">
+        <v>407.14</v>
+      </c>
+      <c r="AF247" t="n">
+        <v>409.2</v>
+      </c>
+      <c r="AG247" t="n">
+        <v>411.63</v>
+      </c>
+      <c r="AH247" t="n">
+        <v>416.27</v>
+      </c>
+      <c r="AI247" t="n">
+        <v>421.44</v>
+      </c>
+      <c r="AJ247" t="n">
+        <v>412.1</v>
+      </c>
+      <c r="AK247" t="n">
+        <v>402.61</v>
+      </c>
+      <c r="AL247" t="n">
+        <v>402.2</v>
+      </c>
+      <c r="AM247" t="n">
+        <v>406.94</v>
+      </c>
+      <c r="AN247" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="n">
+        <v>383.48</v>
+      </c>
+      <c r="C248" t="n">
+        <v>395.41</v>
+      </c>
+      <c r="D248" t="n">
+        <v>397.27</v>
+      </c>
+      <c r="E248" t="n">
+        <v>408.88</v>
+      </c>
+      <c r="F248" t="n">
+        <v>407.74</v>
+      </c>
+      <c r="G248" t="n">
+        <v>407.55</v>
+      </c>
+      <c r="H248" t="n">
+        <v>416.72</v>
+      </c>
+      <c r="I248" t="n">
+        <v>417.6</v>
+      </c>
+      <c r="J248" t="n">
+        <v>415.54</v>
+      </c>
+      <c r="K248" t="n">
+        <v>414.29</v>
+      </c>
+      <c r="L248" t="n">
+        <v>416</v>
+      </c>
+      <c r="M248" t="n">
+        <v>417.07</v>
+      </c>
+      <c r="N248" t="n">
+        <v>412.71</v>
+      </c>
+      <c r="O248" t="n">
+        <v>409.55</v>
+      </c>
+      <c r="P248" t="n">
+        <v>406.31</v>
+      </c>
+      <c r="Q248" t="n">
+        <v>405.23</v>
+      </c>
+      <c r="R248" t="n">
+        <v>406.15</v>
+      </c>
+      <c r="S248" t="n">
+        <v>403.35</v>
+      </c>
+      <c r="T248" t="n">
+        <v>405.54</v>
+      </c>
+      <c r="U248" t="n">
+        <v>411.05</v>
+      </c>
+      <c r="V248" t="n">
+        <v>412.62</v>
+      </c>
+      <c r="W248" t="n">
+        <v>414.71</v>
+      </c>
+      <c r="X248" t="n">
+        <v>413.11</v>
+      </c>
+      <c r="Y248" t="n">
+        <v>414.76</v>
+      </c>
+      <c r="Z248" t="n">
+        <v>415</v>
+      </c>
+      <c r="AA248" t="n">
+        <v>409.65</v>
+      </c>
+      <c r="AB248" t="n">
+        <v>408.92</v>
+      </c>
+      <c r="AC248" t="n">
+        <v>407.21</v>
+      </c>
+      <c r="AD248" t="n">
+        <v>406.9</v>
+      </c>
+      <c r="AE248" t="n">
+        <v>409.72</v>
+      </c>
+      <c r="AF248" t="n">
+        <v>411.55</v>
+      </c>
+      <c r="AG248" t="n">
+        <v>414.25</v>
+      </c>
+      <c r="AH248" t="n">
+        <v>419.52</v>
+      </c>
+      <c r="AI248" t="n">
+        <v>423.25</v>
+      </c>
+      <c r="AJ248" t="n">
+        <v>414.54</v>
+      </c>
+      <c r="AK248" t="n">
+        <v>405.01</v>
+      </c>
+      <c r="AL248" t="n">
+        <v>403.81</v>
+      </c>
+      <c r="AM248" t="n">
+        <v>409.31</v>
+      </c>
+      <c r="AN248" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31456,7 +31708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B257"/>
+  <dimension ref="A1:B259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34029,6 +34281,26 @@
       </c>
       <c r="B257" t="n">
         <v>-0.64</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B258" t="n">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B259" t="n">
+        <v>-0.37</v>
       </c>
     </row>
   </sheetData>
@@ -34197,28 +34469,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.007932760040202054</v>
+        <v>-0.002746687651212147</v>
       </c>
       <c r="J2" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K2" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L2" t="n">
-        <v>4.618782981458125e-05</v>
+        <v>5.621338918460062e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>7.557513747291508</v>
+        <v>7.547207340374223</v>
       </c>
       <c r="N2" t="n">
-        <v>86.30230001748176</v>
+        <v>85.99001000082249</v>
       </c>
       <c r="O2" t="n">
-        <v>9.289903122071928</v>
+        <v>9.273079855194956</v>
       </c>
       <c r="P2" t="n">
-        <v>388.7360272501724</v>
+        <v>388.8328604827544</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34275,28 +34547,28 @@
         <v>0.0723</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1812353472878894</v>
+        <v>0.165949735946051</v>
       </c>
       <c r="J3" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K3" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02490142505563941</v>
+        <v>0.02116002001427775</v>
       </c>
       <c r="M3" t="n">
-        <v>7.364863658411762</v>
+        <v>7.391668802415793</v>
       </c>
       <c r="N3" t="n">
-        <v>81.65023945200895</v>
+        <v>81.79328722995643</v>
       </c>
       <c r="O3" t="n">
-        <v>9.036052205028971</v>
+        <v>9.04396413250055</v>
       </c>
       <c r="P3" t="n">
-        <v>398.0803390237485</v>
+        <v>398.2189684783017</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34353,28 +34625,28 @@
         <v>0.0752</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1619080706137632</v>
+        <v>0.1501214096807501</v>
       </c>
       <c r="J4" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K4" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01891975721796224</v>
+        <v>0.01653611016065648</v>
       </c>
       <c r="M4" t="n">
-        <v>7.29571860575988</v>
+        <v>7.291386910355804</v>
       </c>
       <c r="N4" t="n">
-        <v>86.29254935281725</v>
+        <v>86.05561948013572</v>
       </c>
       <c r="O4" t="n">
-        <v>9.289378308197877</v>
+        <v>9.276616812186203</v>
       </c>
       <c r="P4" t="n">
-        <v>399.3585858335262</v>
+        <v>399.4654913002708</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34431,28 +34703,28 @@
         <v>0.0809</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1479664385872003</v>
+        <v>0.1361166165988345</v>
       </c>
       <c r="J5" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K5" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01539925661394059</v>
+        <v>0.01324720162365345</v>
       </c>
       <c r="M5" t="n">
-        <v>7.798857298483393</v>
+        <v>7.785507351720637</v>
       </c>
       <c r="N5" t="n">
-        <v>88.6764292017759</v>
+        <v>88.42563197481324</v>
       </c>
       <c r="O5" t="n">
-        <v>9.416816298610476</v>
+        <v>9.403490414458519</v>
       </c>
       <c r="P5" t="n">
-        <v>411.397549363379</v>
+        <v>411.5050003142408</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34509,28 +34781,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1509682267445364</v>
+        <v>0.1417369513700297</v>
       </c>
       <c r="J6" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K6" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01529176434270518</v>
+        <v>0.0137232763192433</v>
       </c>
       <c r="M6" t="n">
-        <v>7.67516687451326</v>
+        <v>7.658256652158014</v>
       </c>
       <c r="N6" t="n">
-        <v>92.96991485009369</v>
+        <v>92.50789770385701</v>
       </c>
       <c r="O6" t="n">
-        <v>9.642090792462685</v>
+        <v>9.618102604144802</v>
       </c>
       <c r="P6" t="n">
-        <v>408.3536850300267</v>
+        <v>408.4373859263736</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34587,28 +34859,28 @@
         <v>0.0759</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1022015590573533</v>
+        <v>0.09275097943402023</v>
       </c>
       <c r="J7" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K7" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0082816803909741</v>
+        <v>0.006937622853662506</v>
       </c>
       <c r="M7" t="n">
-        <v>7.390831114525863</v>
+        <v>7.368636734902979</v>
       </c>
       <c r="N7" t="n">
-        <v>79.23302981889952</v>
+        <v>78.89954736442245</v>
       </c>
       <c r="O7" t="n">
-        <v>8.90129371602238</v>
+        <v>8.882541717572874</v>
       </c>
       <c r="P7" t="n">
-        <v>409.4265561835172</v>
+        <v>409.5122434434887</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34665,28 +34937,28 @@
         <v>0.0924</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0219293252638632</v>
+        <v>-0.02935506524893202</v>
       </c>
       <c r="J8" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K8" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004837551129064366</v>
+        <v>0.0008808146158590935</v>
       </c>
       <c r="M8" t="n">
-        <v>6.516681468957945</v>
+        <v>6.495982115422193</v>
       </c>
       <c r="N8" t="n">
-        <v>62.94136817119256</v>
+        <v>62.62828903278978</v>
       </c>
       <c r="O8" t="n">
-        <v>7.933559615405468</v>
+        <v>7.913803701936875</v>
       </c>
       <c r="P8" t="n">
-        <v>420.6125085373071</v>
+        <v>420.6798325298868</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -34743,28 +35015,28 @@
         <v>0.09080000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05050620513637558</v>
+        <v>-0.05768594317324396</v>
       </c>
       <c r="J9" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K9" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002631933305792589</v>
+        <v>0.003487868884039735</v>
       </c>
       <c r="M9" t="n">
-        <v>6.381782553059991</v>
+        <v>6.361182340687559</v>
       </c>
       <c r="N9" t="n">
-        <v>61.36452680864165</v>
+        <v>61.0423635211051</v>
       </c>
       <c r="O9" t="n">
-        <v>7.833551353545954</v>
+        <v>7.812961251734523</v>
       </c>
       <c r="P9" t="n">
-        <v>422.5325258210672</v>
+        <v>422.5976419275208</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -34821,28 +35093,28 @@
         <v>0.0839</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.04338241168471681</v>
+        <v>-0.05262471089699271</v>
       </c>
       <c r="J10" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L10" t="n">
-        <v>0.001999768137187496</v>
+        <v>0.002983335906280082</v>
       </c>
       <c r="M10" t="n">
-        <v>6.365384981035838</v>
+        <v>6.353195154522417</v>
       </c>
       <c r="N10" t="n">
-        <v>59.62463237234376</v>
+        <v>59.42218455009024</v>
       </c>
       <c r="O10" t="n">
-        <v>7.721698800933883</v>
+        <v>7.708578633580268</v>
       </c>
       <c r="P10" t="n">
-        <v>421.9620009276169</v>
+        <v>422.0458326731464</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -34899,28 +35171,28 @@
         <v>0.067</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.06849935293604152</v>
+        <v>-0.07844497188665295</v>
       </c>
       <c r="J11" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K11" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00418621098614369</v>
+        <v>0.005561943486181886</v>
       </c>
       <c r="M11" t="n">
-        <v>6.92618649177435</v>
+        <v>6.908621181700313</v>
       </c>
       <c r="N11" t="n">
-        <v>70.85610813461918</v>
+        <v>70.63993543322076</v>
       </c>
       <c r="O11" t="n">
-        <v>8.417607031372942</v>
+        <v>8.404756714695599</v>
       </c>
       <c r="P11" t="n">
-        <v>420.36787435614</v>
+        <v>420.4580650539446</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -34977,28 +35249,28 @@
         <v>0.0711</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.1248664531287186</v>
+        <v>-0.130920762378348</v>
       </c>
       <c r="J12" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K12" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L12" t="n">
-        <v>0.01321995496968598</v>
+        <v>0.01476679482065379</v>
       </c>
       <c r="M12" t="n">
-        <v>7.142143920531124</v>
+        <v>7.109807819319979</v>
       </c>
       <c r="N12" t="n">
-        <v>73.88040503236203</v>
+        <v>73.42412115104906</v>
       </c>
       <c r="O12" t="n">
-        <v>8.595371139884655</v>
+        <v>8.56878761267013</v>
       </c>
       <c r="P12" t="n">
-        <v>421.4758216413455</v>
+        <v>421.530718022341</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35055,28 +35327,28 @@
         <v>0.0689</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07305673657325386</v>
+        <v>-0.07942726045780414</v>
       </c>
       <c r="J13" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K13" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L13" t="n">
-        <v>0.005535020092398368</v>
+        <v>0.006646925983581076</v>
       </c>
       <c r="M13" t="n">
-        <v>6.268092940007238</v>
+        <v>6.243774443419899</v>
       </c>
       <c r="N13" t="n">
-        <v>60.87488630569432</v>
+        <v>60.53281492284108</v>
       </c>
       <c r="O13" t="n">
-        <v>7.802235981159139</v>
+        <v>7.780283730227393</v>
       </c>
       <c r="P13" t="n">
-        <v>421.5251478529698</v>
+        <v>421.5829150920318</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35133,28 +35405,28 @@
         <v>0.0677</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.08194957896422216</v>
+        <v>-0.0898865970280395</v>
       </c>
       <c r="J14" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K14" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L14" t="n">
-        <v>0.008297288863934438</v>
+        <v>0.01011763272770261</v>
       </c>
       <c r="M14" t="n">
-        <v>5.906212603245481</v>
+        <v>5.894677395399994</v>
       </c>
       <c r="N14" t="n">
-        <v>50.95491454566947</v>
+        <v>50.75320373195448</v>
       </c>
       <c r="O14" t="n">
-        <v>7.138271117411377</v>
+        <v>7.124128278740809</v>
       </c>
       <c r="P14" t="n">
-        <v>419.0684929729132</v>
+        <v>419.1404801188327</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35211,28 +35483,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1393261335966032</v>
+        <v>-0.1456194388685303</v>
       </c>
       <c r="J15" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K15" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02485763605367486</v>
+        <v>0.0275325450008167</v>
       </c>
       <c r="M15" t="n">
-        <v>5.529430290836632</v>
+        <v>5.513034456530872</v>
       </c>
       <c r="N15" t="n">
-        <v>48.34156472032595</v>
+        <v>48.087957429602</v>
       </c>
       <c r="O15" t="n">
-        <v>6.952809843532753</v>
+        <v>6.934548105652018</v>
       </c>
       <c r="P15" t="n">
-        <v>416.1805857174388</v>
+        <v>416.2376591992693</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35289,28 +35561,28 @@
         <v>0.0746</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1322786143585905</v>
+        <v>-0.1406939954144404</v>
       </c>
       <c r="J16" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K16" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0241634533349574</v>
+        <v>0.02762389619635486</v>
       </c>
       <c r="M16" t="n">
-        <v>5.429100296564533</v>
+        <v>5.426803396093671</v>
       </c>
       <c r="N16" t="n">
-        <v>44.85849356079898</v>
+        <v>44.73725939660704</v>
       </c>
       <c r="O16" t="n">
-        <v>6.697648360491836</v>
+        <v>6.688591734932476</v>
       </c>
       <c r="P16" t="n">
-        <v>414.0082290499195</v>
+        <v>414.0845512450427</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35367,28 +35639,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1664635482421771</v>
+        <v>-0.1801483820882738</v>
       </c>
       <c r="J17" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K17" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03562365839162784</v>
+        <v>0.04172947968491558</v>
       </c>
       <c r="M17" t="n">
-        <v>5.524514789927566</v>
+        <v>5.537179420344637</v>
       </c>
       <c r="N17" t="n">
-        <v>47.62046797883267</v>
+        <v>47.84921269646822</v>
       </c>
       <c r="O17" t="n">
-        <v>6.900758507499931</v>
+        <v>6.91731253424827</v>
       </c>
       <c r="P17" t="n">
-        <v>417.6719916940382</v>
+        <v>417.7961221896251</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35445,28 +35717,28 @@
         <v>0.055</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.204602785282093</v>
+        <v>-0.2138693139600919</v>
       </c>
       <c r="J18" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K18" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L18" t="n">
-        <v>0.03612506286478312</v>
+        <v>0.03991423968774621</v>
       </c>
       <c r="M18" t="n">
-        <v>6.731141398799693</v>
+        <v>6.71836350031794</v>
       </c>
       <c r="N18" t="n">
-        <v>70.90591947897785</v>
+        <v>70.63956659190305</v>
       </c>
       <c r="O18" t="n">
-        <v>8.420565270751</v>
+        <v>8.40473477225207</v>
       </c>
       <c r="P18" t="n">
-        <v>415.6362147127666</v>
+        <v>415.7202482067244</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35523,28 +35795,28 @@
         <v>0.0479</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1406829290022802</v>
+        <v>0.1268188023626021</v>
       </c>
       <c r="J19" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K19" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L19" t="n">
-        <v>0.009482859157424417</v>
+        <v>0.007832563294706385</v>
       </c>
       <c r="M19" t="n">
-        <v>9.054578186846724</v>
+        <v>9.044180766406395</v>
       </c>
       <c r="N19" t="n">
-        <v>131.2359538941242</v>
+        <v>130.8028651606232</v>
       </c>
       <c r="O19" t="n">
-        <v>11.45582619866957</v>
+        <v>11.4369080244891</v>
       </c>
       <c r="P19" t="n">
-        <v>407.5961716896438</v>
+        <v>407.7219267196775</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35601,28 +35873,28 @@
         <v>0.055</v>
       </c>
       <c r="I20" t="n">
-        <v>0.007038635148527836</v>
+        <v>-0.006341518067713269</v>
       </c>
       <c r="J20" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K20" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L20" t="n">
-        <v>4.248546977370093e-05</v>
+        <v>3.489195299599679e-05</v>
       </c>
       <c r="M20" t="n">
-        <v>7.019695292975627</v>
+        <v>7.029825709685096</v>
       </c>
       <c r="N20" t="n">
-        <v>74.08289986027698</v>
+        <v>74.06526600709827</v>
       </c>
       <c r="O20" t="n">
-        <v>8.607142374811572</v>
+        <v>8.606117940575661</v>
       </c>
       <c r="P20" t="n">
-        <v>413.2834845798675</v>
+        <v>413.4044845747699</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35679,28 +35951,28 @@
         <v>0.0839</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.07275768459341313</v>
+        <v>-0.07947393493699625</v>
       </c>
       <c r="J21" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K21" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L21" t="n">
-        <v>0.007540659870333033</v>
+        <v>0.009126855432293857</v>
       </c>
       <c r="M21" t="n">
-        <v>5.466805954147992</v>
+        <v>5.454393936708037</v>
       </c>
       <c r="N21" t="n">
-        <v>44.26456096219681</v>
+        <v>44.06190489656687</v>
       </c>
       <c r="O21" t="n">
-        <v>6.653161726742918</v>
+        <v>6.637914197740648</v>
       </c>
       <c r="P21" t="n">
-        <v>416.2041720433354</v>
+        <v>416.265034415307</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -35757,28 +36029,28 @@
         <v>0.0838</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.05515733467855588</v>
+        <v>-0.06299885593195421</v>
       </c>
       <c r="J22" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K22" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L22" t="n">
-        <v>0.006686266423167941</v>
+        <v>0.008811468921775756</v>
       </c>
       <c r="M22" t="n">
-        <v>4.224934971266312</v>
+        <v>4.228293968970713</v>
       </c>
       <c r="N22" t="n">
-        <v>28.71470483123568</v>
+        <v>28.68733659230239</v>
       </c>
       <c r="O22" t="n">
-        <v>5.358610345158125</v>
+        <v>5.356056066949113</v>
       </c>
       <c r="P22" t="n">
-        <v>418.3235516299979</v>
+        <v>418.3946181044727</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -35835,28 +36107,28 @@
         <v>0.1942</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.09080429229828287</v>
+        <v>-0.09677686979879219</v>
       </c>
       <c r="J23" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K23" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L23" t="n">
-        <v>0.01836186705382925</v>
+        <v>0.02111469095315555</v>
       </c>
       <c r="M23" t="n">
-        <v>4.089973639787621</v>
+        <v>4.082977718380509</v>
       </c>
       <c r="N23" t="n">
-        <v>28.00543921246204</v>
+        <v>27.90019076378347</v>
       </c>
       <c r="O23" t="n">
-        <v>5.292016554439531</v>
+        <v>5.282063116224896</v>
       </c>
       <c r="P23" t="n">
-        <v>420.1141715261011</v>
+        <v>420.1682965905825</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -35913,28 +36185,28 @@
         <v>0.0851</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.09786399059901595</v>
+        <v>-0.1073495693058697</v>
       </c>
       <c r="J24" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K24" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L24" t="n">
-        <v>0.01671700359709416</v>
+        <v>0.02025280994514156</v>
       </c>
       <c r="M24" t="n">
-        <v>4.862676548435877</v>
+        <v>4.866000894741736</v>
       </c>
       <c r="N24" t="n">
-        <v>35.78994122825979</v>
+        <v>35.82170898225218</v>
       </c>
       <c r="O24" t="n">
-        <v>5.982469492463776</v>
+        <v>5.985123973841493</v>
       </c>
       <c r="P24" t="n">
-        <v>419.9309640165437</v>
+        <v>420.0169172154261</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -35991,28 +36263,28 @@
         <v>0.2</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.08877996604239857</v>
+        <v>-0.09488797459039484</v>
       </c>
       <c r="J25" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K25" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L25" t="n">
-        <v>0.01604765624044124</v>
+        <v>0.01856353700066959</v>
       </c>
       <c r="M25" t="n">
-        <v>4.35061833355426</v>
+        <v>4.346320884466079</v>
       </c>
       <c r="N25" t="n">
-        <v>30.70346931502235</v>
+        <v>30.58727330570568</v>
       </c>
       <c r="O25" t="n">
-        <v>5.541071134268387</v>
+        <v>5.530576218234921</v>
       </c>
       <c r="P25" t="n">
-        <v>419.8554493531786</v>
+        <v>419.910797125005</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -36069,28 +36341,28 @@
         <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.07901427137887451</v>
+        <v>-0.08624408070214626</v>
       </c>
       <c r="J26" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K26" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L26" t="n">
-        <v>0.01509812686160461</v>
+        <v>0.01815989200973223</v>
       </c>
       <c r="M26" t="n">
-        <v>3.84676758515691</v>
+        <v>3.853644061289155</v>
       </c>
       <c r="N26" t="n">
-        <v>25.87474166985091</v>
+        <v>25.84062723970401</v>
       </c>
       <c r="O26" t="n">
-        <v>5.086722094812229</v>
+        <v>5.083367706521338</v>
       </c>
       <c r="P26" t="n">
-        <v>420.9207988685844</v>
+        <v>420.9863202991755</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -36147,28 +36419,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.06993277585771449</v>
+        <v>-0.08217726091828359</v>
       </c>
       <c r="J27" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K27" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01067332313184588</v>
+        <v>0.01471307743941364</v>
       </c>
       <c r="M27" t="n">
-        <v>4.0973000132721</v>
+        <v>4.124392158901453</v>
       </c>
       <c r="N27" t="n">
-        <v>28.80027577579435</v>
+        <v>29.05892005230942</v>
       </c>
       <c r="O27" t="n">
-        <v>5.366588839830601</v>
+        <v>5.390632620788531</v>
       </c>
       <c r="P27" t="n">
-        <v>418.7371943055256</v>
+        <v>418.8481731173799</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -36225,28 +36497,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1153302801701613</v>
+        <v>-0.1250336192251703</v>
       </c>
       <c r="J28" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K28" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L28" t="n">
-        <v>0.02744264510568928</v>
+        <v>0.03236241859830868</v>
       </c>
       <c r="M28" t="n">
-        <v>4.276184689888354</v>
+        <v>4.289474467764632</v>
       </c>
       <c r="N28" t="n">
-        <v>29.94821879859844</v>
+        <v>30.03601485347828</v>
       </c>
       <c r="O28" t="n">
-        <v>5.472496578217153</v>
+        <v>5.480512280205043</v>
       </c>
       <c r="P28" t="n">
-        <v>416.517060034398</v>
+        <v>416.6049896063807</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -36303,28 +36575,28 @@
         <v>0.1413</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.145852100473387</v>
+        <v>-0.1528008021588375</v>
       </c>
       <c r="J29" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K29" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L29" t="n">
-        <v>0.05054291193603144</v>
+        <v>0.05587230333785753</v>
       </c>
       <c r="M29" t="n">
-        <v>3.850781588204146</v>
+        <v>3.852322860139509</v>
       </c>
       <c r="N29" t="n">
-        <v>25.54394531277557</v>
+        <v>25.50338312376221</v>
       </c>
       <c r="O29" t="n">
-        <v>5.054101830471519</v>
+        <v>5.050087437239301</v>
       </c>
       <c r="P29" t="n">
-        <v>414.4796149438885</v>
+        <v>414.5425015940143</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -36381,28 +36653,28 @@
         <v>0.0956</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1265215303729594</v>
+        <v>-0.1366418236590559</v>
       </c>
       <c r="J30" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K30" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L30" t="n">
-        <v>0.03118008458573773</v>
+        <v>0.03648745950523913</v>
       </c>
       <c r="M30" t="n">
-        <v>4.078587446752754</v>
+        <v>4.094734860687906</v>
       </c>
       <c r="N30" t="n">
-        <v>31.50764860852415</v>
+        <v>31.59022403260612</v>
       </c>
       <c r="O30" t="n">
-        <v>5.613167431007572</v>
+        <v>5.620518128483006</v>
       </c>
       <c r="P30" t="n">
-        <v>416.0017667098671</v>
+        <v>416.0935378665022</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -36459,28 +36731,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.1405496139507131</v>
+        <v>-0.154556800914096</v>
       </c>
       <c r="J31" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K31" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L31" t="n">
-        <v>0.03829026852739636</v>
+        <v>0.04588418777400227</v>
       </c>
       <c r="M31" t="n">
-        <v>4.194020909082943</v>
+        <v>4.220681358798473</v>
       </c>
       <c r="N31" t="n">
-        <v>31.42941261520693</v>
+        <v>31.82628488637522</v>
       </c>
       <c r="O31" t="n">
-        <v>5.606194129282978</v>
+        <v>5.641478962681259</v>
       </c>
       <c r="P31" t="n">
-        <v>421.1671351150522</v>
+        <v>421.2941494429099</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -36537,28 +36809,28 @@
         <v>0.0849</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1292287066315607</v>
+        <v>-0.1412406729801323</v>
       </c>
       <c r="J32" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K32" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0386439654905909</v>
+        <v>0.04587418213733352</v>
       </c>
       <c r="M32" t="n">
-        <v>3.836083420650277</v>
+        <v>3.866737910429001</v>
       </c>
       <c r="N32" t="n">
-        <v>26.31733558989691</v>
+        <v>26.58450208849786</v>
       </c>
       <c r="O32" t="n">
-        <v>5.13004245497997</v>
+        <v>5.156016106307065</v>
       </c>
       <c r="P32" t="n">
-        <v>421.5269362954852</v>
+        <v>421.6358574088608</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -36615,28 +36887,28 @@
         <v>0.0956</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.04895574981901817</v>
+        <v>-0.06043213403394681</v>
       </c>
       <c r="J33" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K33" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L33" t="n">
-        <v>0.005427525194508842</v>
+        <v>0.008276802840948783</v>
       </c>
       <c r="M33" t="n">
-        <v>3.842969883298862</v>
+        <v>3.858563826933197</v>
       </c>
       <c r="N33" t="n">
-        <v>27.82039890823049</v>
+        <v>28.03724807171006</v>
       </c>
       <c r="O33" t="n">
-        <v>5.274504612589745</v>
+        <v>5.295021064331101</v>
       </c>
       <c r="P33" t="n">
-        <v>421.6149796194376</v>
+        <v>421.7190415343364</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -36693,28 +36965,28 @@
         <v>0.0655</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1550830027278247</v>
+        <v>-0.1676446218832452</v>
       </c>
       <c r="J34" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K34" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L34" t="n">
-        <v>0.04101251713346343</v>
+        <v>0.04780171468268457</v>
       </c>
       <c r="M34" t="n">
-        <v>4.330944217863988</v>
+        <v>4.35571872608811</v>
       </c>
       <c r="N34" t="n">
-        <v>35.62429414882867</v>
+        <v>35.87028539721397</v>
       </c>
       <c r="O34" t="n">
-        <v>5.968609063159412</v>
+        <v>5.989180694987752</v>
       </c>
       <c r="P34" t="n">
-        <v>430.0898913616422</v>
+        <v>430.2037908843218</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -36771,28 +37043,28 @@
         <v>0.0956</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1444394737097919</v>
+        <v>-0.1572089979566876</v>
       </c>
       <c r="J35" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K35" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L35" t="n">
-        <v>0.03599328765950693</v>
+        <v>0.04253235631651331</v>
       </c>
       <c r="M35" t="n">
-        <v>4.345524074017476</v>
+        <v>4.36214754884563</v>
       </c>
       <c r="N35" t="n">
-        <v>35.51765767068956</v>
+        <v>35.76818811134868</v>
       </c>
       <c r="O35" t="n">
-        <v>5.95966925849829</v>
+        <v>5.980651144428061</v>
       </c>
       <c r="P35" t="n">
-        <v>434.3890879132726</v>
+        <v>434.5047566741105</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -36849,28 +37121,28 @@
         <v>0.1394</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.1984103059514691</v>
+        <v>-0.2104715888691528</v>
       </c>
       <c r="J36" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K36" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L36" t="n">
-        <v>0.06439852117673706</v>
+        <v>0.07229241328191427</v>
       </c>
       <c r="M36" t="n">
-        <v>4.799567361035094</v>
+        <v>4.808812317905144</v>
       </c>
       <c r="N36" t="n">
-        <v>36.35443843570152</v>
+        <v>36.5462502401302</v>
       </c>
       <c r="O36" t="n">
-        <v>6.029464191427089</v>
+        <v>6.045349472125677</v>
       </c>
       <c r="P36" t="n">
-        <v>426.3492521535338</v>
+        <v>426.4585002568573</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -36927,28 +37199,28 @@
         <v>0.1224</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.1662040680428202</v>
+        <v>-0.179758573497312</v>
       </c>
       <c r="J37" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K37" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="L37" t="n">
-        <v>0.03393579296052263</v>
+        <v>0.03974618634943505</v>
       </c>
       <c r="M37" t="n">
-        <v>5.094548924415968</v>
+        <v>5.109166173856412</v>
       </c>
       <c r="N37" t="n">
-        <v>49.8141404376816</v>
+        <v>50.0197438519159</v>
       </c>
       <c r="O37" t="n">
-        <v>7.057913320357626</v>
+        <v>7.072463775228255</v>
       </c>
       <c r="P37" t="n">
-        <v>416.9371331241651</v>
+        <v>417.0600433313094</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -37005,28 +37277,28 @@
         <v>0.1069</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.08462491230520647</v>
+        <v>-0.1014257153766794</v>
       </c>
       <c r="J38" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K38" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L38" t="n">
-        <v>0.008534286591950213</v>
+        <v>0.01223765048791814</v>
       </c>
       <c r="M38" t="n">
-        <v>5.595167069475509</v>
+        <v>5.61260247180682</v>
       </c>
       <c r="N38" t="n">
-        <v>52.85693674197693</v>
+        <v>53.35406716301281</v>
       </c>
       <c r="O38" t="n">
-        <v>7.270277624821278</v>
+        <v>7.30438684374074</v>
       </c>
       <c r="P38" t="n">
-        <v>416.0506612666358</v>
+        <v>416.2029375538506</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -37083,28 +37355,28 @@
         <v>0.2</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1750485832762727</v>
+        <v>-0.1901774407235576</v>
       </c>
       <c r="J39" t="n">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="K39" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L39" t="n">
-        <v>0.03243431367062632</v>
+        <v>0.03829568404181205</v>
       </c>
       <c r="M39" t="n">
-        <v>5.870747353996865</v>
+        <v>5.888554945074659</v>
       </c>
       <c r="N39" t="n">
-        <v>58.07483655690921</v>
+        <v>58.36153155562925</v>
       </c>
       <c r="O39" t="n">
-        <v>7.620684782675977</v>
+        <v>7.639471942197919</v>
       </c>
       <c r="P39" t="n">
-        <v>422.50077178711</v>
+        <v>422.6378875386383</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -37142,7 +37414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN246"/>
+  <dimension ref="A1:AN248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86721,6 +86993,410 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-29 22:17:05+00:00</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>-34.86133779326362,173.29568010845233</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>-34.86156185879364,173.29648028591106</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>-34.861627596964986,173.29733632366165</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>-34.8616746316942,173.29819911808548</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>-34.86167590468068,173.29904454382353</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>-34.86167061771123,173.29995435047053</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>-34.861615512118256,173.30084124555466</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>-34.86155946829425,173.3016990461712</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>-34.86150087792839,173.30258134590733</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>-34.861462058022326,173.30348432830633</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>-34.86138106027908,173.30438648260477</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>-34.86131863006755,173.3052781159601</t>
+        </is>
+      </c>
+      <c r="N247" t="inlineStr">
+        <is>
+          <t>-34.86127943670505,173.30616935061173</t>
+        </is>
+      </c>
+      <c r="O247" t="inlineStr">
+        <is>
+          <t>-34.86124355635163,173.3070697661144</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>-34.86121364305715,173.3079843675702</t>
+        </is>
+      </c>
+      <c r="Q247" t="inlineStr">
+        <is>
+          <t>-34.86120197580378,173.3088826563848</t>
+        </is>
+      </c>
+      <c r="R247" t="inlineStr">
+        <is>
+          <t>-34.86115541109285,173.3097599263948</t>
+        </is>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>-34.86108694297866,173.31065675732253</t>
+        </is>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>-34.86101099937472,173.31156076833005</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>-34.86092879622184,173.31245268572374</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>-34.86085401520161,173.31333751991667</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>-34.86077074230011,173.31421264072958</t>
+        </is>
+      </c>
+      <c r="X247" t="inlineStr">
+        <is>
+          <t>-34.860700688770834,173.31509652662166</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>-34.86057679081772,173.31598860275142</t>
+        </is>
+      </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t>-34.86048255625411,173.3168696132785</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>-34.86040664409443,173.3177527482505</t>
+        </is>
+      </c>
+      <c r="AB247" t="inlineStr">
+        <is>
+          <t>-34.86031268388571,173.31864822969672</t>
+        </is>
+      </c>
+      <c r="AC247" t="inlineStr">
+        <is>
+          <t>-34.86020540303643,173.3195506922328</t>
+        </is>
+      </c>
+      <c r="AD247" t="inlineStr">
+        <is>
+          <t>-34.860126878706104,173.3204553792317</t>
+        </is>
+      </c>
+      <c r="AE247" t="inlineStr">
+        <is>
+          <t>-34.86003931802662,173.32133542912047</t>
+        </is>
+      </c>
+      <c r="AF247" t="inlineStr">
+        <is>
+          <t>-34.85991074430849,173.32221162111242</t>
+        </is>
+      </c>
+      <c r="AG247" t="inlineStr">
+        <is>
+          <t>-34.85978803663293,173.32311163110379</t>
+        </is>
+      </c>
+      <c r="AH247" t="inlineStr">
+        <is>
+          <t>-34.859674028898155,173.32400506997908</t>
+        </is>
+      </c>
+      <c r="AI247" t="inlineStr">
+        <is>
+          <t>-34.859550869576765,173.3248271163811</t>
+        </is>
+      </c>
+      <c r="AJ247" t="inlineStr">
+        <is>
+          <t>-34.859430236913234,173.32566500460624</t>
+        </is>
+      </c>
+      <c r="AK247" t="inlineStr">
+        <is>
+          <t>-34.85929849163485,173.3265849191116</t>
+        </is>
+      </c>
+      <c r="AL247" t="inlineStr">
+        <is>
+          <t>-34.85918295227034,173.3275113536414</t>
+        </is>
+      </c>
+      <c r="AM247" t="inlineStr">
+        <is>
+          <t>-34.85906570733731,173.32841127567482</t>
+        </is>
+      </c>
+      <c r="AN247" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-15 22:16:42+00:00</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>-34.86131519441763,173.29569352347997</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>-34.86152164418606,173.29649544904098</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>-34.86160665803121,173.29734093727367</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>-34.861653810028095,173.29820158541975</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>-34.86165237167034,173.29904410083734</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>-34.861643927102214,173.29995467974643</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>-34.86158918252243,173.3008408836987</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>-34.86154113004316,173.30169728177077</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>-34.861488947447434,173.30257985792286</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>-34.861423809188835,173.30348000057654</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>-34.86134985848772,173.3043836190476</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>-34.86129022965658,173.30527529415642</t>
+        </is>
+      </c>
+      <c r="N248" t="inlineStr">
+        <is>
+          <t>-34.86126291690251,173.30616747075024</t>
+        </is>
+      </c>
+      <c r="O248" t="inlineStr">
+        <is>
+          <t>-34.86122352637542,173.30706760321547</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>-34.86119157969805,173.30798297909706</t>
+        </is>
+      </c>
+      <c r="Q248" t="inlineStr">
+        <is>
+          <t>-34.86118801731825,173.3088817787737</t>
+        </is>
+      </c>
+      <c r="R248" t="inlineStr">
+        <is>
+          <t>-34.86112111672146,173.30975599570365</t>
+        </is>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>-34.86107050457186,173.31065499957847</t>
+        </is>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>-34.86099939077142,173.3115598613627</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>-34.8609090032977,173.31245105294965</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>-34.86083955006504,173.31333601441685</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>-34.860755519754,173.31421044410263</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>-34.860667107032064,173.31509085117085</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>-34.86055550075747,173.31598531557034</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>-34.86046783174267,173.31686701907478</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>-34.860395260846374,173.31775043035117</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>-34.8602823169869,173.3186423603619</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>-34.860186083448866,173.3195476853707</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>-34.86011315408532,173.32045366864426</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>-34.8600162416335,173.3213318396906</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>-34.859889777596784,173.32220788849529</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>-34.85976457717579,173.3231082339167</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>-34.85964489632998,173.32400119605586</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>-34.859534895689585,173.32482304994213</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>-34.859409161232534,173.3256573375338</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>-34.85927738165045,173.32657913261048</t>
+        </is>
+      </c>
+      <c r="AL248" t="inlineStr">
+        <is>
+          <t>-34.859168555500865,173.3275090798384</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>-34.85904444736759,173.32840862917422</t>
+        </is>
+      </c>
+      <c r="AN248" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0028/nzd0028.xlsx
+++ b/data/nzd0028/nzd0028.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN248"/>
+  <dimension ref="A1:AN249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31697,6 +31697,132 @@
         </is>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="n">
+        <v>385.12</v>
+      </c>
+      <c r="C249" t="n">
+        <v>398.81</v>
+      </c>
+      <c r="D249" t="n">
+        <v>397.23</v>
+      </c>
+      <c r="E249" t="n">
+        <v>409.34</v>
+      </c>
+      <c r="F249" t="n">
+        <v>408.88</v>
+      </c>
+      <c r="G249" t="n">
+        <v>409.05</v>
+      </c>
+      <c r="H249" t="n">
+        <v>418.54</v>
+      </c>
+      <c r="I249" t="n">
+        <v>417.55</v>
+      </c>
+      <c r="J249" t="n">
+        <v>415.68</v>
+      </c>
+      <c r="K249" t="n">
+        <v>415.23</v>
+      </c>
+      <c r="L249" t="n">
+        <v>416.86</v>
+      </c>
+      <c r="M249" t="n">
+        <v>418.05</v>
+      </c>
+      <c r="N249" t="n">
+        <v>413.39</v>
+      </c>
+      <c r="O249" t="n">
+        <v>409.51</v>
+      </c>
+      <c r="P249" t="n">
+        <v>406.19</v>
+      </c>
+      <c r="Q249" t="n">
+        <v>401.21</v>
+      </c>
+      <c r="R249" t="n">
+        <v>405.84</v>
+      </c>
+      <c r="S249" t="n">
+        <v>404.29</v>
+      </c>
+      <c r="T249" t="n">
+        <v>404.59</v>
+      </c>
+      <c r="U249" t="n">
+        <v>411.94</v>
+      </c>
+      <c r="V249" t="n">
+        <v>413.07</v>
+      </c>
+      <c r="W249" t="n">
+        <v>414.88</v>
+      </c>
+      <c r="X249" t="n">
+        <v>413.84</v>
+      </c>
+      <c r="Y249" t="n">
+        <v>417.7</v>
+      </c>
+      <c r="Z249" t="n">
+        <v>417.18</v>
+      </c>
+      <c r="AA249" t="n">
+        <v>410.87</v>
+      </c>
+      <c r="AB249" t="n">
+        <v>410.29</v>
+      </c>
+      <c r="AC249" t="n">
+        <v>409.15</v>
+      </c>
+      <c r="AD249" t="n">
+        <v>406.58</v>
+      </c>
+      <c r="AE249" t="n">
+        <v>409.33</v>
+      </c>
+      <c r="AF249" t="n">
+        <v>413.74</v>
+      </c>
+      <c r="AG249" t="n">
+        <v>414.07</v>
+      </c>
+      <c r="AH249" t="n">
+        <v>420.52</v>
+      </c>
+      <c r="AI249" t="n">
+        <v>424.55</v>
+      </c>
+      <c r="AJ249" t="n">
+        <v>416.1</v>
+      </c>
+      <c r="AK249" t="n">
+        <v>407.8</v>
+      </c>
+      <c r="AL249" t="n">
+        <v>404.3</v>
+      </c>
+      <c r="AM249" t="n">
+        <v>410.43</v>
+      </c>
+      <c r="AN249" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -31708,7 +31834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B259"/>
+  <dimension ref="A1:B260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -34301,6 +34427,16 @@
       </c>
       <c r="B259" t="n">
         <v>-0.37</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:20:00+00:00</t>
+        </is>
+      </c>
+      <c r="B260" t="n">
+        <v>-0.24</v>
       </c>
     </row>
   </sheetData>
@@ -34469,28 +34605,28 @@
         <v>0.08400000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.002746687651212147</v>
+        <v>-0.005563376424605991</v>
       </c>
       <c r="J2" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K2" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L2" t="n">
-        <v>5.621338918460062e-06</v>
+        <v>2.327076071828582e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>7.547207340374223</v>
+        <v>7.530131862442905</v>
       </c>
       <c r="N2" t="n">
-        <v>85.99001000082249</v>
+        <v>85.69603626661674</v>
       </c>
       <c r="O2" t="n">
-        <v>9.273079855194956</v>
+        <v>9.257215362441167</v>
       </c>
       <c r="P2" t="n">
-        <v>388.8328604827544</v>
+        <v>388.8585088218242</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -34547,28 +34683,28 @@
         <v>0.0723</v>
       </c>
       <c r="I3" t="n">
-        <v>0.165949735946051</v>
+        <v>0.1629805994103774</v>
       </c>
       <c r="J3" t="n">
+        <v>248</v>
+      </c>
+      <c r="K3" t="n">
         <v>247</v>
       </c>
-      <c r="K3" t="n">
-        <v>246</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.02116002001427775</v>
+        <v>0.02060385011330512</v>
       </c>
       <c r="M3" t="n">
-        <v>7.391668802415793</v>
+        <v>7.378393746158682</v>
       </c>
       <c r="N3" t="n">
-        <v>81.79328722995643</v>
+        <v>81.52098526023929</v>
       </c>
       <c r="O3" t="n">
-        <v>9.04396413250055</v>
+        <v>9.028897233895139</v>
       </c>
       <c r="P3" t="n">
-        <v>398.2189684783017</v>
+        <v>398.2460126182132</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -34625,28 +34761,28 @@
         <v>0.0752</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1501214096807501</v>
+        <v>0.1452964636611364</v>
       </c>
       <c r="J4" t="n">
+        <v>248</v>
+      </c>
+      <c r="K4" t="n">
         <v>247</v>
       </c>
-      <c r="K4" t="n">
-        <v>246</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.01653611016065648</v>
+        <v>0.01562620914529422</v>
       </c>
       <c r="M4" t="n">
-        <v>7.291386910355804</v>
+        <v>7.284384712467892</v>
       </c>
       <c r="N4" t="n">
-        <v>86.05561948013572</v>
+        <v>85.86260997414897</v>
       </c>
       <c r="O4" t="n">
-        <v>9.276616812186203</v>
+        <v>9.266207960873151</v>
       </c>
       <c r="P4" t="n">
-        <v>399.4654913002708</v>
+        <v>399.5094389307187</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -34703,28 +34839,28 @@
         <v>0.0809</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1361166165988345</v>
+        <v>0.1316320092057406</v>
       </c>
       <c r="J5" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K5" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01324720162365345</v>
+        <v>0.01249920879899891</v>
       </c>
       <c r="M5" t="n">
-        <v>7.785507351720637</v>
+        <v>7.773133984957741</v>
       </c>
       <c r="N5" t="n">
-        <v>88.42563197481324</v>
+        <v>88.202821952045</v>
       </c>
       <c r="O5" t="n">
-        <v>9.403490414458519</v>
+        <v>9.391635744216499</v>
       </c>
       <c r="P5" t="n">
-        <v>411.5050003142408</v>
+        <v>411.5458364662857</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -34781,28 +34917,28 @@
         <v>0.07530000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1417369513700297</v>
+        <v>0.1391588443210942</v>
       </c>
       <c r="J6" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K6" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0137232763192433</v>
+        <v>0.01335532772218151</v>
       </c>
       <c r="M6" t="n">
-        <v>7.658256652158014</v>
+        <v>7.64005770952101</v>
       </c>
       <c r="N6" t="n">
-        <v>92.50789770385701</v>
+        <v>92.17908281598629</v>
       </c>
       <c r="O6" t="n">
-        <v>9.618102604144802</v>
+        <v>9.600993845221769</v>
       </c>
       <c r="P6" t="n">
-        <v>408.4373859263736</v>
+        <v>408.4608617765896</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -34859,28 +34995,28 @@
         <v>0.0759</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09275097943402023</v>
+        <v>0.09047794582975534</v>
       </c>
       <c r="J7" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K7" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L7" t="n">
-        <v>0.006937622853662506</v>
+        <v>0.006664633299829248</v>
       </c>
       <c r="M7" t="n">
-        <v>7.368636734902979</v>
+        <v>7.347963274359282</v>
       </c>
       <c r="N7" t="n">
-        <v>78.89954736442245</v>
+        <v>78.61576300582345</v>
       </c>
       <c r="O7" t="n">
-        <v>8.882541717572874</v>
+        <v>8.866553050978911</v>
       </c>
       <c r="P7" t="n">
-        <v>409.5122434434887</v>
+        <v>409.5329413413714</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -34937,28 +35073,28 @@
         <v>0.0924</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.02935506524893202</v>
+        <v>-0.03040624038275646</v>
       </c>
       <c r="J8" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K8" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0008808146158590935</v>
+        <v>0.0009540002444560214</v>
       </c>
       <c r="M8" t="n">
-        <v>6.495982115422193</v>
+        <v>6.474270838631458</v>
       </c>
       <c r="N8" t="n">
-        <v>62.62828903278978</v>
+        <v>62.38310377049774</v>
       </c>
       <c r="O8" t="n">
-        <v>7.913803701936875</v>
+        <v>7.89829752354884</v>
       </c>
       <c r="P8" t="n">
-        <v>420.6798325298868</v>
+        <v>420.6894043705917</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -35015,28 +35151,28 @@
         <v>0.09080000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.05768594317324396</v>
+        <v>-0.06039797571081878</v>
       </c>
       <c r="J9" t="n">
+        <v>248</v>
+      </c>
+      <c r="K9" t="n">
         <v>247</v>
       </c>
-      <c r="K9" t="n">
-        <v>246</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.003487868884039735</v>
+        <v>0.003855976870871913</v>
       </c>
       <c r="M9" t="n">
-        <v>6.361182340687559</v>
+        <v>6.347130171975981</v>
       </c>
       <c r="N9" t="n">
-        <v>61.0423635211051</v>
+        <v>60.84432359636041</v>
       </c>
       <c r="O9" t="n">
-        <v>7.812961251734523</v>
+        <v>7.800277148689039</v>
       </c>
       <c r="P9" t="n">
-        <v>422.5976419275208</v>
+        <v>422.6223442564669</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -35093,28 +35229,28 @@
         <v>0.0839</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.05262471089699271</v>
+        <v>-0.0564665930482416</v>
       </c>
       <c r="J10" t="n">
+        <v>248</v>
+      </c>
+      <c r="K10" t="n">
         <v>247</v>
       </c>
-      <c r="K10" t="n">
-        <v>246</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.002983335906280082</v>
+        <v>0.003460637071569406</v>
       </c>
       <c r="M10" t="n">
-        <v>6.353195154522417</v>
+        <v>6.343791005445033</v>
       </c>
       <c r="N10" t="n">
-        <v>59.42218455009024</v>
+        <v>59.28013173450269</v>
       </c>
       <c r="O10" t="n">
-        <v>7.708578633580268</v>
+        <v>7.699359176873274</v>
       </c>
       <c r="P10" t="n">
-        <v>422.0458326731464</v>
+        <v>422.0808261458861</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -35171,28 +35307,28 @@
         <v>0.067</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.07844497188665295</v>
+        <v>-0.08087400040511558</v>
       </c>
       <c r="J11" t="n">
+        <v>248</v>
+      </c>
+      <c r="K11" t="n">
         <v>247</v>
       </c>
-      <c r="K11" t="n">
-        <v>246</v>
-      </c>
       <c r="L11" t="n">
-        <v>0.005561943486181886</v>
+        <v>0.005963159509905003</v>
       </c>
       <c r="M11" t="n">
-        <v>6.908621181700313</v>
+        <v>6.890248876110682</v>
       </c>
       <c r="N11" t="n">
-        <v>70.63993543322076</v>
+        <v>70.39332726643603</v>
       </c>
       <c r="O11" t="n">
-        <v>8.404756714695599</v>
+        <v>8.390073138324603</v>
       </c>
       <c r="P11" t="n">
-        <v>420.4580650539446</v>
+        <v>420.4801896636797</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -35249,28 +35385,28 @@
         <v>0.0711</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.130920762378348</v>
+        <v>-0.1318339193597219</v>
       </c>
       <c r="J12" t="n">
+        <v>248</v>
+      </c>
+      <c r="K12" t="n">
         <v>247</v>
       </c>
-      <c r="K12" t="n">
-        <v>246</v>
-      </c>
       <c r="L12" t="n">
-        <v>0.01476679482065379</v>
+        <v>0.01511189207999519</v>
       </c>
       <c r="M12" t="n">
-        <v>7.109807819319979</v>
+        <v>7.084851808213186</v>
       </c>
       <c r="N12" t="n">
-        <v>73.42412115104906</v>
+        <v>73.13242345764903</v>
       </c>
       <c r="O12" t="n">
-        <v>8.56878761267013</v>
+        <v>8.551749730765572</v>
       </c>
       <c r="P12" t="n">
-        <v>421.530718022341</v>
+        <v>421.539035438825</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -35327,28 +35463,28 @@
         <v>0.0689</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.07942726045780414</v>
+        <v>-0.08052290052742399</v>
       </c>
       <c r="J13" t="n">
+        <v>248</v>
+      </c>
+      <c r="K13" t="n">
         <v>247</v>
       </c>
-      <c r="K13" t="n">
-        <v>246</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.006646925983581076</v>
+        <v>0.006895008899673649</v>
       </c>
       <c r="M13" t="n">
-        <v>6.243774443419899</v>
+        <v>6.223015213478357</v>
       </c>
       <c r="N13" t="n">
-        <v>60.53281492284108</v>
+        <v>60.2957556034198</v>
       </c>
       <c r="O13" t="n">
-        <v>7.780283730227393</v>
+        <v>7.76503416627511</v>
       </c>
       <c r="P13" t="n">
-        <v>421.5829150920318</v>
+        <v>421.592894640961</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -35405,28 +35541,28 @@
         <v>0.0677</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.0898865970280395</v>
+        <v>-0.09247974493400997</v>
       </c>
       <c r="J14" t="n">
+        <v>248</v>
+      </c>
+      <c r="K14" t="n">
         <v>247</v>
       </c>
-      <c r="K14" t="n">
-        <v>246</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.01011763272770261</v>
+        <v>0.01079641151091115</v>
       </c>
       <c r="M14" t="n">
-        <v>5.894677395399994</v>
+        <v>5.882586229188475</v>
       </c>
       <c r="N14" t="n">
-        <v>50.75320373195448</v>
+        <v>50.5926103964779</v>
       </c>
       <c r="O14" t="n">
-        <v>7.124128278740809</v>
+        <v>7.112848261876384</v>
       </c>
       <c r="P14" t="n">
-        <v>419.1404801188327</v>
+        <v>419.1640995967305</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -35483,28 +35619,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1456194388685303</v>
+        <v>-0.1478145164515924</v>
       </c>
       <c r="J15" t="n">
+        <v>248</v>
+      </c>
+      <c r="K15" t="n">
         <v>247</v>
       </c>
-      <c r="K15" t="n">
-        <v>246</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.0275325450008167</v>
+        <v>0.02859282299077648</v>
       </c>
       <c r="M15" t="n">
-        <v>5.513034456530872</v>
+        <v>5.500552522515797</v>
       </c>
       <c r="N15" t="n">
-        <v>48.087957429602</v>
+        <v>47.92543175042167</v>
       </c>
       <c r="O15" t="n">
-        <v>6.934548105652018</v>
+        <v>6.922819638732593</v>
       </c>
       <c r="P15" t="n">
-        <v>416.2376591992693</v>
+        <v>416.2576528858376</v>
       </c>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
@@ -35561,28 +35697,28 @@
         <v>0.0746</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1406939954144404</v>
+        <v>-0.1438990922551372</v>
       </c>
       <c r="J16" t="n">
+        <v>248</v>
+      </c>
+      <c r="K16" t="n">
         <v>247</v>
       </c>
-      <c r="K16" t="n">
-        <v>246</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.02762389619635486</v>
+        <v>0.02908763141148552</v>
       </c>
       <c r="M16" t="n">
-        <v>5.426803396093671</v>
+        <v>5.420593706492299</v>
       </c>
       <c r="N16" t="n">
-        <v>44.73725939660704</v>
+        <v>44.6247064096993</v>
       </c>
       <c r="O16" t="n">
-        <v>6.688591734932476</v>
+        <v>6.680172633225829</v>
       </c>
       <c r="P16" t="n">
-        <v>414.0845512450427</v>
+        <v>414.1137446103015</v>
       </c>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
@@ -35639,28 +35775,28 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.1801483820882738</v>
+        <v>-0.189260268996486</v>
       </c>
       <c r="J17" t="n">
+        <v>248</v>
+      </c>
+      <c r="K17" t="n">
         <v>247</v>
       </c>
-      <c r="K17" t="n">
-        <v>246</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.04172947968491558</v>
+        <v>0.0457744563237652</v>
       </c>
       <c r="M17" t="n">
-        <v>5.537179420344637</v>
+        <v>5.555332869262342</v>
       </c>
       <c r="N17" t="n">
-        <v>47.84921269646822</v>
+        <v>48.20968981239928</v>
       </c>
       <c r="O17" t="n">
-        <v>6.91731253424827</v>
+        <v>6.94331979764718</v>
       </c>
       <c r="P17" t="n">
-        <v>417.7961221896251</v>
+        <v>417.8791170743133</v>
       </c>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
@@ -35717,28 +35853,28 @@
         <v>0.055</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2138693139600919</v>
+        <v>-0.2171022981037814</v>
       </c>
       <c r="J18" t="n">
+        <v>248</v>
+      </c>
+      <c r="K18" t="n">
         <v>247</v>
       </c>
-      <c r="K18" t="n">
-        <v>246</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.03991423968774621</v>
+        <v>0.04142165042801982</v>
       </c>
       <c r="M18" t="n">
-        <v>6.71836350031794</v>
+        <v>6.705795235480499</v>
       </c>
       <c r="N18" t="n">
-        <v>70.63956659190305</v>
+        <v>70.42334439199142</v>
       </c>
       <c r="O18" t="n">
-        <v>8.40473477225207</v>
+        <v>8.3918617953343</v>
       </c>
       <c r="P18" t="n">
-        <v>415.7202482067244</v>
+        <v>415.7496955812261</v>
       </c>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
@@ -35795,28 +35931,28 @@
         <v>0.0479</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1268188023626021</v>
+        <v>0.121551204271217</v>
       </c>
       <c r="J19" t="n">
+        <v>248</v>
+      </c>
+      <c r="K19" t="n">
         <v>247</v>
       </c>
-      <c r="K19" t="n">
-        <v>246</v>
-      </c>
       <c r="L19" t="n">
-        <v>0.007832563294706385</v>
+        <v>0.007258881491499558</v>
       </c>
       <c r="M19" t="n">
-        <v>9.044180766406395</v>
+        <v>9.031287613577266</v>
       </c>
       <c r="N19" t="n">
-        <v>130.8028651606232</v>
+        <v>130.4585130133108</v>
       </c>
       <c r="O19" t="n">
-        <v>11.4369080244891</v>
+        <v>11.42184367837832</v>
       </c>
       <c r="P19" t="n">
-        <v>407.7219267196775</v>
+        <v>407.7699062107075</v>
       </c>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
@@ -35873,28 +36009,28 @@
         <v>0.055</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.006341518067713269</v>
+        <v>-0.013041439929704</v>
       </c>
       <c r="J20" t="n">
+        <v>248</v>
+      </c>
+      <c r="K20" t="n">
         <v>247</v>
       </c>
-      <c r="K20" t="n">
-        <v>246</v>
-      </c>
       <c r="L20" t="n">
-        <v>3.489195299599679e-05</v>
+        <v>0.0001483853934565182</v>
       </c>
       <c r="M20" t="n">
-        <v>7.029825709685096</v>
+        <v>7.035046831987623</v>
       </c>
       <c r="N20" t="n">
-        <v>74.06526600709827</v>
+        <v>74.06370281838718</v>
       </c>
       <c r="O20" t="n">
-        <v>8.606117940575661</v>
+        <v>8.606027121639066</v>
       </c>
       <c r="P20" t="n">
-        <v>413.4044845747699</v>
+        <v>413.4653243496138</v>
       </c>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
@@ -35951,28 +36087,28 @@
         <v>0.0839</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.07947393493699625</v>
+        <v>-0.08118065305507106</v>
       </c>
       <c r="J21" t="n">
+        <v>248</v>
+      </c>
+      <c r="K21" t="n">
         <v>247</v>
       </c>
-      <c r="K21" t="n">
-        <v>246</v>
-      </c>
       <c r="L21" t="n">
-        <v>0.009126855432293857</v>
+        <v>0.009606269783923982</v>
       </c>
       <c r="M21" t="n">
-        <v>5.454393936708037</v>
+        <v>5.440355157485502</v>
       </c>
       <c r="N21" t="n">
-        <v>44.06190489656687</v>
+        <v>43.90297499103803</v>
       </c>
       <c r="O21" t="n">
-        <v>6.637914197740648</v>
+        <v>6.625932009237495</v>
       </c>
       <c r="P21" t="n">
-        <v>416.265034415307</v>
+        <v>416.2805677027292</v>
       </c>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
@@ -36029,28 +36165,28 @@
         <v>0.0838</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.06299885593195421</v>
+        <v>-0.065816345039661</v>
       </c>
       <c r="J22" t="n">
+        <v>248</v>
+      </c>
+      <c r="K22" t="n">
         <v>247</v>
       </c>
-      <c r="K22" t="n">
-        <v>246</v>
-      </c>
       <c r="L22" t="n">
-        <v>0.008811468921775756</v>
+        <v>0.009683748588516616</v>
       </c>
       <c r="M22" t="n">
-        <v>4.228293968970713</v>
+        <v>4.22462765669458</v>
       </c>
       <c r="N22" t="n">
-        <v>28.68733659230239</v>
+        <v>28.62422179528171</v>
       </c>
       <c r="O22" t="n">
-        <v>5.356056066949113</v>
+        <v>5.350160913026982</v>
       </c>
       <c r="P22" t="n">
-        <v>418.3946181044727</v>
+        <v>418.4202608088277</v>
       </c>
       <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
@@ -36107,28 +36243,28 @@
         <v>0.1942</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.09677686979879219</v>
+        <v>-0.09887340253735762</v>
       </c>
       <c r="J23" t="n">
+        <v>248</v>
+      </c>
+      <c r="K23" t="n">
         <v>247</v>
       </c>
-      <c r="K23" t="n">
-        <v>246</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.02111469095315555</v>
+        <v>0.0222043885025085</v>
       </c>
       <c r="M23" t="n">
-        <v>4.082977718380509</v>
+        <v>4.075803556443216</v>
       </c>
       <c r="N23" t="n">
-        <v>27.90019076378347</v>
+        <v>27.81659656631996</v>
       </c>
       <c r="O23" t="n">
-        <v>5.282063116224896</v>
+        <v>5.27414415486721</v>
       </c>
       <c r="P23" t="n">
-        <v>420.1682965905825</v>
+        <v>420.1873776826933</v>
       </c>
       <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
@@ -36185,28 +36321,28 @@
         <v>0.0851</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1073495693058697</v>
+        <v>-0.1099073637858001</v>
       </c>
       <c r="J24" t="n">
+        <v>248</v>
+      </c>
+      <c r="K24" t="n">
         <v>247</v>
       </c>
-      <c r="K24" t="n">
-        <v>246</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.02025280994514156</v>
+        <v>0.02138383529073717</v>
       </c>
       <c r="M24" t="n">
-        <v>4.866000894741736</v>
+        <v>4.857836623709773</v>
       </c>
       <c r="N24" t="n">
-        <v>35.82170898225218</v>
+        <v>35.72038511993578</v>
       </c>
       <c r="O24" t="n">
-        <v>5.985123973841493</v>
+        <v>5.976653337774894</v>
       </c>
       <c r="P24" t="n">
-        <v>420.0169172154261</v>
+        <v>420.0401963711362</v>
       </c>
       <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
@@ -36263,28 +36399,28 @@
         <v>0.2</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.09488797459039484</v>
+        <v>-0.09464009767040604</v>
       </c>
       <c r="J25" t="n">
+        <v>248</v>
+      </c>
+      <c r="K25" t="n">
         <v>247</v>
       </c>
-      <c r="K25" t="n">
-        <v>246</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.01856353700066959</v>
+        <v>0.01864353003479513</v>
       </c>
       <c r="M25" t="n">
-        <v>4.346320884466079</v>
+        <v>4.330038350544759</v>
       </c>
       <c r="N25" t="n">
-        <v>30.58727330570568</v>
+        <v>30.46384863624782</v>
       </c>
       <c r="O25" t="n">
-        <v>5.530576218234921</v>
+        <v>5.519406547469377</v>
       </c>
       <c r="P25" t="n">
-        <v>419.910797125005</v>
+        <v>419.9085411324056</v>
       </c>
       <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
@@ -36341,28 +36477,28 @@
         <v>0.2</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.08624408070214626</v>
+        <v>-0.08740621817698666</v>
       </c>
       <c r="J26" t="n">
+        <v>248</v>
+      </c>
+      <c r="K26" t="n">
         <v>247</v>
       </c>
-      <c r="K26" t="n">
-        <v>246</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.01815989200973223</v>
+        <v>0.01881388124768191</v>
       </c>
       <c r="M26" t="n">
-        <v>3.853644061289155</v>
+        <v>3.844129919814281</v>
       </c>
       <c r="N26" t="n">
-        <v>25.84062723970401</v>
+        <v>25.74503121437334</v>
       </c>
       <c r="O26" t="n">
-        <v>5.083367706521338</v>
+        <v>5.073956169930259</v>
       </c>
       <c r="P26" t="n">
-        <v>420.9863202991755</v>
+        <v>420.9968972159081</v>
       </c>
       <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
@@ -36419,28 +36555,28 @@
         <v>0.08309999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.08217726091828359</v>
+        <v>-0.08665087161825973</v>
       </c>
       <c r="J27" t="n">
+        <v>248</v>
+      </c>
+      <c r="K27" t="n">
         <v>247</v>
       </c>
-      <c r="K27" t="n">
-        <v>246</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.01471307743941364</v>
+        <v>0.01641252721949182</v>
       </c>
       <c r="M27" t="n">
-        <v>4.124392158901453</v>
+        <v>4.129935478777516</v>
       </c>
       <c r="N27" t="n">
-        <v>29.05892005230942</v>
+        <v>29.07496272249401</v>
       </c>
       <c r="O27" t="n">
-        <v>5.390632620788531</v>
+        <v>5.392120429153453</v>
       </c>
       <c r="P27" t="n">
-        <v>418.8481731173799</v>
+        <v>418.888888616959</v>
       </c>
       <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
@@ -36497,28 +36633,28 @@
         <v>0.07580000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.1250336192251703</v>
+        <v>-0.1273353348002634</v>
       </c>
       <c r="J28" t="n">
+        <v>248</v>
+      </c>
+      <c r="K28" t="n">
         <v>247</v>
       </c>
-      <c r="K28" t="n">
-        <v>246</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.03236241859830868</v>
+        <v>0.03379924893798669</v>
       </c>
       <c r="M28" t="n">
-        <v>4.289474467764632</v>
+        <v>4.283469098178341</v>
       </c>
       <c r="N28" t="n">
-        <v>30.03601485347828</v>
+        <v>29.9498020178062</v>
       </c>
       <c r="O28" t="n">
-        <v>5.480512280205043</v>
+        <v>5.472641228676168</v>
       </c>
       <c r="P28" t="n">
-        <v>416.6049896063807</v>
+        <v>416.6259381210848</v>
       </c>
       <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
@@ -36575,28 +36711,28 @@
         <v>0.1413</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.1528008021588375</v>
+        <v>-0.1538198023226858</v>
       </c>
       <c r="J29" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K29" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L29" t="n">
-        <v>0.05587230333785753</v>
+        <v>0.05707716300420529</v>
       </c>
       <c r="M29" t="n">
-        <v>3.852322860139509</v>
+        <v>3.841719537007223</v>
       </c>
       <c r="N29" t="n">
-        <v>25.50338312376221</v>
+        <v>25.40628841368365</v>
       </c>
       <c r="O29" t="n">
-        <v>5.050087437239301</v>
+        <v>5.040465098945102</v>
       </c>
       <c r="P29" t="n">
-        <v>414.5425015940143</v>
+        <v>414.5517640681122</v>
       </c>
       <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
@@ -36653,28 +36789,28 @@
         <v>0.0956</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1366418236590559</v>
+        <v>-0.1411821077314758</v>
       </c>
       <c r="J30" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K30" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L30" t="n">
-        <v>0.03648745950523913</v>
+        <v>0.03905496661817576</v>
       </c>
       <c r="M30" t="n">
-        <v>4.094734860687906</v>
+        <v>4.100615103357337</v>
       </c>
       <c r="N30" t="n">
-        <v>31.59022403260612</v>
+        <v>31.59993056007024</v>
       </c>
       <c r="O30" t="n">
-        <v>5.620518128483006</v>
+        <v>5.621381552614111</v>
       </c>
       <c r="P30" t="n">
-        <v>416.0935378665022</v>
+        <v>416.1348810019111</v>
       </c>
       <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
@@ -36731,28 +36867,28 @@
         <v>0.07099999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.154556800914096</v>
+        <v>-0.1606188366860592</v>
       </c>
       <c r="J31" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K31" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L31" t="n">
-        <v>0.04588418777400227</v>
+        <v>0.04946510272368598</v>
       </c>
       <c r="M31" t="n">
-        <v>4.220681358798473</v>
+        <v>4.230310682334066</v>
       </c>
       <c r="N31" t="n">
-        <v>31.82628488637522</v>
+        <v>31.94233300701404</v>
       </c>
       <c r="O31" t="n">
-        <v>5.641478962681259</v>
+        <v>5.651754860838714</v>
       </c>
       <c r="P31" t="n">
-        <v>421.2941494429099</v>
+        <v>421.3493494175758</v>
       </c>
       <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
@@ -36809,28 +36945,28 @@
         <v>0.0849</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.1412406729801323</v>
+        <v>-0.1444292048931063</v>
       </c>
       <c r="J32" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K32" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L32" t="n">
-        <v>0.04587418213733352</v>
+        <v>0.04819280376010393</v>
       </c>
       <c r="M32" t="n">
-        <v>3.866737910429001</v>
+        <v>3.867540607994898</v>
       </c>
       <c r="N32" t="n">
-        <v>26.58450208849786</v>
+        <v>26.54491637843318</v>
       </c>
       <c r="O32" t="n">
-        <v>5.156016106307065</v>
+        <v>5.152175887761712</v>
       </c>
       <c r="P32" t="n">
-        <v>421.6358574088608</v>
+        <v>421.6648916949386</v>
       </c>
       <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
@@ -36887,28 +37023,28 @@
         <v>0.0956</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.06043213403394681</v>
+        <v>-0.0651028061313393</v>
       </c>
       <c r="J33" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K33" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L33" t="n">
-        <v>0.008276802840948783</v>
+        <v>0.009635360924205361</v>
       </c>
       <c r="M33" t="n">
-        <v>3.858563826933197</v>
+        <v>3.863771050141239</v>
       </c>
       <c r="N33" t="n">
-        <v>28.03724807171006</v>
+        <v>28.06926788080046</v>
       </c>
       <c r="O33" t="n">
-        <v>5.295021064331101</v>
+        <v>5.298043778679114</v>
       </c>
       <c r="P33" t="n">
-        <v>421.7190415343364</v>
+        <v>421.7615719632464</v>
       </c>
       <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
@@ -36965,28 +37101,28 @@
         <v>0.0655</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.1676446218832452</v>
+        <v>-0.1716711330948949</v>
       </c>
       <c r="J34" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K34" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L34" t="n">
-        <v>0.04780171468268457</v>
+        <v>0.05032516585064106</v>
       </c>
       <c r="M34" t="n">
-        <v>4.35571872608811</v>
+        <v>4.357385740291796</v>
       </c>
       <c r="N34" t="n">
-        <v>35.87028539721397</v>
+        <v>35.83346392644672</v>
       </c>
       <c r="O34" t="n">
-        <v>5.989180694987752</v>
+        <v>5.986105906718216</v>
       </c>
       <c r="P34" t="n">
-        <v>430.2037908843218</v>
+        <v>430.2404556822932</v>
       </c>
       <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
@@ -37043,28 +37179,28 @@
         <v>0.0956</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.1572089979566876</v>
+        <v>-0.1616644127468497</v>
       </c>
       <c r="J35" t="n">
+        <v>248</v>
+      </c>
+      <c r="K35" t="n">
         <v>247</v>
       </c>
-      <c r="K35" t="n">
-        <v>246</v>
-      </c>
       <c r="L35" t="n">
-        <v>0.04253235631651331</v>
+        <v>0.0451216243903646</v>
       </c>
       <c r="M35" t="n">
-        <v>4.36214754884563</v>
+        <v>4.36313096772701</v>
       </c>
       <c r="N35" t="n">
-        <v>35.76818811134868</v>
+        <v>35.75602587289128</v>
       </c>
       <c r="O35" t="n">
-        <v>5.980651144428061</v>
+        <v>5.979634259124155</v>
       </c>
       <c r="P35" t="n">
-        <v>434.5047566741105</v>
+        <v>434.5452837619641</v>
       </c>
       <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
@@ -37121,28 +37257,28 @@
         <v>0.1394</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.2104715888691528</v>
+        <v>-0.2141425912590933</v>
       </c>
       <c r="J36" t="n">
+        <v>248</v>
+      </c>
+      <c r="K36" t="n">
         <v>247</v>
       </c>
-      <c r="K36" t="n">
-        <v>246</v>
-      </c>
       <c r="L36" t="n">
-        <v>0.07229241328191427</v>
+        <v>0.07514221406738786</v>
       </c>
       <c r="M36" t="n">
-        <v>4.808812317905144</v>
+        <v>4.803838478178872</v>
       </c>
       <c r="N36" t="n">
-        <v>36.5462502401302</v>
+        <v>36.48834195722341</v>
       </c>
       <c r="O36" t="n">
-        <v>6.045349472125677</v>
+        <v>6.040558083258815</v>
       </c>
       <c r="P36" t="n">
-        <v>426.4585002568573</v>
+        <v>426.4918922177353</v>
       </c>
       <c r="Q36" t="inlineStr"/>
       <c r="R36" t="inlineStr">
@@ -37199,28 +37335,28 @@
         <v>0.1224</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.179758573497312</v>
+        <v>-0.1832093715649088</v>
       </c>
       <c r="J37" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K37" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="L37" t="n">
-        <v>0.03974618634943505</v>
+        <v>0.0415428301154529</v>
       </c>
       <c r="M37" t="n">
-        <v>5.109166173856412</v>
+        <v>5.102755287498467</v>
       </c>
       <c r="N37" t="n">
-        <v>50.0197438519159</v>
+        <v>49.89724083829176</v>
       </c>
       <c r="O37" t="n">
-        <v>7.072463775228255</v>
+        <v>7.063797904689216</v>
       </c>
       <c r="P37" t="n">
-        <v>417.0600433313094</v>
+        <v>417.0914657730556</v>
       </c>
       <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
@@ -37277,28 +37413,28 @@
         <v>0.1069</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.1014257153766794</v>
+        <v>-0.1085388279823673</v>
       </c>
       <c r="J38" t="n">
+        <v>248</v>
+      </c>
+      <c r="K38" t="n">
         <v>247</v>
       </c>
-      <c r="K38" t="n">
-        <v>246</v>
-      </c>
       <c r="L38" t="n">
-        <v>0.01223765048791814</v>
+        <v>0.01403486623007222</v>
       </c>
       <c r="M38" t="n">
-        <v>5.61260247180682</v>
+        <v>5.617033486020001</v>
       </c>
       <c r="N38" t="n">
-        <v>53.35406716301281</v>
+        <v>53.47604758937929</v>
       </c>
       <c r="O38" t="n">
-        <v>7.30438684374074</v>
+        <v>7.312731882776729</v>
       </c>
       <c r="P38" t="n">
-        <v>416.2029375538506</v>
+        <v>416.2676758497653</v>
       </c>
       <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
@@ -37355,28 +37491,28 @@
         <v>0.2</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.1901774407235576</v>
+        <v>-0.1956917921066365</v>
       </c>
       <c r="J39" t="n">
+        <v>248</v>
+      </c>
+      <c r="K39" t="n">
         <v>247</v>
       </c>
-      <c r="K39" t="n">
-        <v>246</v>
-      </c>
       <c r="L39" t="n">
-        <v>0.03829568404181205</v>
+        <v>0.04069650433393113</v>
       </c>
       <c r="M39" t="n">
-        <v>5.888554945074659</v>
+        <v>5.889342664401996</v>
       </c>
       <c r="N39" t="n">
-        <v>58.36153155562925</v>
+        <v>58.32837899435066</v>
       </c>
       <c r="O39" t="n">
-        <v>7.639471942197919</v>
+        <v>7.637301813752726</v>
       </c>
       <c r="P39" t="n">
-        <v>422.6378875386383</v>
+        <v>422.6880750910368</v>
       </c>
       <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
@@ -37414,7 +37550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN248"/>
+  <dimension ref="A1:AN249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87397,6 +87533,208 @@
         </is>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-08 22:16:51+00:00</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>-34.861301910507436,173.2957014090125</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>-34.86149236588373,173.29650648856963</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>-34.8616070129284,173.29734085907688</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>-34.86164968159431,173.29820207463243</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>-34.86164209288419,173.29904390734924</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>-34.861630401455706,173.29995484660918</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>-34.861572771609886,173.30084065815845</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>-34.86154157951009,173.30169732501588</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>-34.86148769160734,173.30257970129296</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>-34.86141536930533,173.30347904563206</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>-34.86134212547886,173.3043829093479</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>-34.86128142193416,173.3052744190405</t>
+        </is>
+      </c>
+      <c r="N249" t="inlineStr">
+        <is>
+          <t>-34.86125681175808,173.306166776019</t>
+        </is>
+      </c>
+      <c r="O249" t="inlineStr">
+        <is>
+          <t>-34.861223885657516,173.30706764201187</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>-34.86119266035238,173.3079830471039</t>
+        </is>
+      </c>
+      <c r="Q249" t="inlineStr">
+        <is>
+          <t>-34.861224219325784,173.3088840549012</t>
+        </is>
+      </c>
+      <c r="R249" t="inlineStr">
+        <is>
+          <t>-34.86112389977255,173.30975631468633</t>
+        </is>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>-34.861062060800016,173.3106540966938</t>
+        </is>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>-34.86100793974284,173.31156052928438</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>-34.86090099616019,173.31245039241855</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>-34.86083550701445,173.31333559362506</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>-34.860753997499394,173.31421022444</t>
+        </is>
+      </c>
+      <c r="X249" t="inlineStr">
+        <is>
+          <t>-34.86066058717315,173.31508974928866</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>-34.86052920127105,173.31598125493727</t>
+        </is>
+      </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t>-34.86044837753952,173.31686359158283</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>-34.86038441118802,173.31774822110398</t>
+        </is>
+      </c>
+      <c r="AB249" t="inlineStr">
+        <is>
+          <t>-34.86027011679577,173.31864000230198</t>
+        </is>
+      </c>
+      <c r="AC249" t="inlineStr">
+        <is>
+          <t>-34.860168731596964,173.3195449847643</t>
+        </is>
+      </c>
+      <c r="AD249" t="inlineStr">
+        <is>
+          <t>-34.86011602459425,173.32045402641415</t>
+        </is>
+      </c>
+      <c r="AE249" t="inlineStr">
+        <is>
+          <t>-34.8600197299255,173.3213323822787</t>
+        </is>
+      </c>
+      <c r="AF249" t="inlineStr">
+        <is>
+          <t>-34.859870238405705,173.3222044100155</t>
+        </is>
+      </c>
+      <c r="AG249" t="inlineStr">
+        <is>
+          <t>-34.85976618889422,173.32310846731116</t>
+        </is>
+      </c>
+      <c r="AH249" t="inlineStr">
+        <is>
+          <t>-34.859635932462794,173.32400000408006</t>
+        </is>
+      </c>
+      <c r="AI249" t="inlineStr">
+        <is>
+          <t>-34.859523422731804,173.3248201292963</t>
+        </is>
+      </c>
+      <c r="AJ249" t="inlineStr">
+        <is>
+          <t>-34.85939568661669,173.32565243563712</t>
+        </is>
+      </c>
+      <c r="AK249" t="inlineStr">
+        <is>
+          <t>-34.85925284129314,173.32657240580664</t>
+        </is>
+      </c>
+      <c r="AL249" t="inlineStr">
+        <is>
+          <t>-34.859164173875364,173.32750838781155</t>
+        </is>
+      </c>
+      <c r="AM249" t="inlineStr">
+        <is>
+          <t>-34.859034400462015,173.3284073785078</t>
+        </is>
+      </c>
+      <c r="AN249" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
